--- a/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
+++ b/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,9 +117,6 @@
       <color theme="0"/>
       <sz val="10"/>
     </font>
-    <font>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -677,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -893,26 +890,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1765,367 +1762,639 @@
       </c>
       <c r="O14" s="88" t="n"/>
     </row>
-    <row r="15" ht="1800" customFormat="1" customHeight="1" s="6">
+    <row r="15" ht="600" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="89" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
         </is>
       </c>
-      <c r="B15" s="89" t="inlineStr">
-        <is>
-          <t>RA 1 RECONOCER VOCABLOS Y EXPRESIONES BÁSICAS EN INGLÉS, DE FORMA ESCRITA Y AUDITIVA, ENMARCADOS EN EL DESEMPEÑO DE FUNCIONES PROPIAS EN EL SECTOR MARÍTIMO Y PORTUARIO.</t>
-        </is>
-      </c>
-      <c r="C15" s="67" t="n"/>
+      <c r="B15" s="90" t="inlineStr">
+        <is>
+          <t>transversal
+Apertura transversal · activación + diagnóstico baseline · NO cubre RAP específico (cobertura via B1-B4 APROPIACIÓN)</t>
+        </is>
+      </c>
+      <c r="C15" s="91" t="inlineStr"/>
       <c r="D15" s="89" t="inlineStr">
         <is>
-          <t>UNIT 1: SHIP OVERVIEW
-PARTS OF THE SHIPS
-TYPES OF MERCHANT VESSELS
-NAVIGATIONAL AND SAFETY-RELATED EQUIPMENT OF THE SHIP
-REVIEW OF DEMONSTRATIVES ADJECTIVES AND VERB TO BE
-SINGULAR AND PLURAL NOUNS
-UNIT 2: THE CREW
-PROFESSIONS IN PORT AND ABOARD
-UNIT 5: INTRODUCING IMO STANDARD MARINE COMMUNICATION PHRASES (SMCP)
-STANDARD SPELLING
-MESSAGE MARKERS
-STANDARD RESPONSES AND ORGANIZATIONAL PHRASES
-COMMANDS (TO: OFFICERS, SAILORS, HELMSMAN, CAPTAINS, ENGINEERS, STEWARD, CRANE OPERATORS)
-REVIEW OF PRESENT SIMPLE TENSE
-IMPERATIVE
-MODAL VERBS: CAN, COULD, SHOULD, MUST FOR REQUEST, PROHIBITION, POSSIBILITY, PERMISSION
-UNIT 3: PLACES IN PORT AND POSITION
-PLACES IN PORT · LOCATIONS
-WEATHER CONDITIONS
-TAG QUESTIONS
-REVIEW OF PRESENT PROGRESSIVE AND PREPOSITIONAL PHRASES OF GEOGRAPHIC LOCATION AND DISTANCE
-UNIT 4: IN PORT
-CONTAINERIZATION
-PACKING, SHIPPING AND CARGO HANDLING
-MANEUVERING (MOORING, DOCKING, DEPARTURE)
-QUANTIFIERS</t>
+          <t>• (N/A — bloque APERTURA: activación + diagnóstico · NO introduce saberes formales nuevos · cobertura via B1-B4 APROPIACIÓN)</t>
         </is>
       </c>
       <c r="E15" s="89" t="inlineStr">
         <is>
-          <t>IDENTIFICAR Y EXTRAER INFORMACIÓN PRECISA EN INGLÉS GENERADA EN EL INTERCAMBIO ORAL Y/O ESCRITO EN ESTE IDIOMA, DADO EN EL CUMPLIMIENTO DE LAS ACCIONES REQUERIDAS A BORDO DEL BUQUE Y EN PUERTO.
-RECONOCER LOS DISTINTOS OFICIOS ENMARCADOS EN LOS CAMPOS MARÍTIMO Y PORTUARIO.
-RECONOCER LA MANERA DE DELETREAR LOS VOCABLOS EN INGLÉS.
-RESPONDER EN INGLÉS EN CONVERSACIONES SENCILLAS Y UTILIZANDO LAS FRASES ESTANDARIZADAS POR LA OMI, EN EL DESEMPEÑO DE LAS OPERACIONES QUE SE GENEREN EN EL CONTEXTO.
-IDENTIFICAR VOCABULARIO COMÚN EN INGLÉS, EN LAS FRASES ESTANDARIZADAS DE LA OMI PARA LA COMUNICACIÓN MARÍTIMA.
-IDENTIFICAR ESTRUCTURAS GRAMATICALES BÁSICAS EN INGLÉS, TALES COMO VERBOS RELACIONADOS CON LAS ACCIONES EMPRENDIDAS DENTRO DE LOS OFICIOS A BORDO DEL BUQUE Y EN PUERTO.
-EXPRESAR E INTERPRETAR ÓRDENES QUE SE DAN EN EL CUMPLIMIENTO DE LAS DISTINTAS FUNCIONES REQUERIDAS EN EL EJERCICIO DE LOS ROLES A BORDO DEL BUQUE Y EN PUERTO.
-EXPRESAR PROHIBICIÓN, PERMISIÓN, POSIBILIDAD O HACER PEDIDOS EN INGLÉS, EN CUANTO A PROCESOS ENMARCADOS EN EL DESEMPEÑO DE LAS OPERACIONES MARÍTIMAS Y PORTUARIAS.
-HABLAR SOBRE UBICACIONES EN INGLÉS QUE PERMITAN AL INTERLOCUTOR CONOCER EL ESPACIO FÍSICO EN EL QUE SE DESEMPEÑAN LAS FUNCIONES A BORDO DEL BUQUE.
-DESCRIBIR ELEMENTOS Y PROCESOS EN INGLÉS, DERIVADOS DE LOS DISTINTOS ROLES QUE SE EJERCEN EN EL CUMPLIMIENTO DE LAS OBLIGACIONES A BORDO DEL BUQUE Y EN PUERTO.</t>
+          <t>• (N/A — bloque APERTURA: NO produce saberes proceso formales · habilita Spark + Gap Analysis activación afectiva)</t>
         </is>
       </c>
       <c r="F15" s="89" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRITERIOS SOFÍA GENERALES:
-• INTERPRETA MENSAJES SENCILLOS DE COMUNICACIÓN EN INGLÉS, SEGÚN CONTEXTO DE LAS OPERACIONES A BORDO Y EN EL PUERTO.
-• IDENTIFICA VOCABLOS BÁSICOS EN INGLÉS RELACIONADOS CON ELEMENTOS FÍSICOS DEL BUQUE Y PUERTO.
-• RESPONDE EN INGLÉS EN CONVERSACIONES SENCILLAS UTILIZANDO LAS FRASES ESTANDARIZADAS POR LA OMI.
-• APLICA REGLAS GRAMATICALES BÁSICAS EN INGLÉS PARA COMUNICACIÓN PUERTO-BUQUE.
-• DESCRIBE EN INGLÉS PROCESOS Y FUNCIONES PROPIAS DEL CONTEXTO MARÍTIMO Y PORTUARIO.
-CRITERIOS ESPECÍFICOS CANON SISTEMA C01-C08:
-• C01: Reconocer vocabulario portuario y partes del barco en textos auténticos adaptados
-  (RAP: RA1 · CEFR: A1.2 · Evidencia: E1 SS3 · Cuestionario No 1)
-• C02: Producir reportes escritos básicos (Inspection Report) aplicando verbo to be · imperativo · plurales · preposición IN sin errores que comprometan la inteligibilidad operativa
-  (RAP: ['RA1', 'RA3'] · CEFR: A1.2-A1.3 · Evidencia: E2 SS4 · Lista de Verificación No 2)
-• C03: Comprender frases estandarizadas SMCP de la OMI en audio auténtico VHF (incluyendo lingua franca B1 no-nativa) e identificar mensajes correctos vs distractores
-  (RAP: RA2 · CEFR: A1.3 · Evidencia: E3 SS5 · Lista de Chequeo No 3)
-• C04: Interactuar oralmente vía VHF respondiendo con SMCP estandarizado y deletreando con NATO Phonetic Alphabet con stress correcto en respuestas críticas (Roger · Wilco · Affirmative · Standby)
-  (RAP: ['RA2', 'RA3'] · CEFR: A1.3-A2.0 · Evidencia: E4-parcial SS6 · Escala de Estimación No 4)
-• C05: Coordinar operaciones tripartitas de berthing aplicando modales · condicional tipo 1 · voz pasiva · presente perfecto en intercambio simultáneo con 3 actores
-  (RAP: RA3 · CEFR: A2.0 · Evidencia: E4-final SS8 · Escala de Estimación No 4)
-• C06: Aplicar las 5 master functions IMARPOR con conectores (and/but/or/because/so/although) en Role Carousel de 5 estaciones
-  (RAP: ['RA3', 'RA4'] · CEFR: A2.0-A2.1 · Evidencia: E5 SS9 · Escala de Estimación No 5)
-• C07: Demostrar dominio integrado de saberes (Reading + Writing + Listening + Vocabulary + Grammar) en Cuestionario Consolidado S6 · 25 ítems · ≥ 70% para PASS
-  (RAP: ['RA1', 'RA2', 'RA3', 'RA4'] · CEFR: consolidación A1.2-A2.0 · Evidencia: E6 SS6 · Cuestionario No 6)
-• C08: Describir funciones profesionales del rol portuario aplicando estructuras ocupacionales (responsible for · specialize in · coordinate · supervise · report to) y tag questions producción ante panel eva
-  (RAP: RA4 · CEFR: A2.1 · Evidencia: E-Misión SS12 · Rúbrica ABP capstone (6 criterios C01-C13))
-</t>
-        </is>
-      </c>
-      <c r="G15" s="90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. [S1·PM-2.1·actitudinal·1.0h] Reflexionar sobre el miedo operacional al inglés VHF mediante video testimonio dramatizado de Manuel Padilla activando interés afectivo en operaciones cold chain Puerto Antioquia.
-2. [S1·PM-2.1·actitudinal·1.0h] Reflexionar sobre el arquetipo destino cold chain coordinator mediante artefacto ICA Phytosanitary Certificate firmado por Mariana Suárez activando proyección afectiva operaciones bilingües.
-3. [S1·PM-2.2·cognitiva·1.5h] Diagnosticar el reconocimiento léxico portuario reefer mediante galería visual diagnóstica y KWL bilingüe activando saberes operacionales previos.
-4. [S1·PM-2.2·cognitiva·1.5h] Diagnosticar el baseline auditivo SMCP mediante audio VHF auténtico de 90 segundos y checklist binaria triangulada sin enseñar frases nuevas.
-5. [S2·PM-2.5·cognitiva·2.5h] Mapear 20 términos canon RA1 sobre partes del barco, tipos de vessels, equipamiento y profesiones portuarias mediante Word Wall Active y mapa semántico colaborativo.
-6. [S2·PM-2.10·cognitiva·2.5h] Inducir el patrón canon de verb to be, demostrativos this/that/these/those y plurales -s/-es a partir de un corpus reefer y formular la regla en propias palabras.
-7. [S3·PM-2.3·cognitiva·4.0h] Reconocer vocabulario portuario y partes del barco en el Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia' aplicando DRTA + K-W-L + Story Map.
-8. [S3·PM-2.6·cognitiva·1.5h] Reforzar comprensión auditiva del vocabulario portuario y bay counts en audio Reefer Yard Walk de Yurlenis.
-10. [S4·PM-2.4·procedimental·4.5h] Producir un Inspection Report técnico de una página sobre el walk-around del bay 14 del MV CARIBBEAN STAR aplicando vocabulario portuario y estructuras gramaticales A1.2-A1.3.
-12. [S4·PM-4.2·cognitiva·1.0h] Diseñar el banco proto de ítems Vocabulary y Reading cara RA1 del Cuestionario Consolidado E6 mediante curaduría colaborativa de 6-8 ítems sobre vocabulario portuario.
-13. [S5·PM-2.6·procedimental·3.0h] Identificar mensajes correctos y distractores SMCP en audio VHF auténtico de Captain Lim Wei-Ming según protocolo OMI.
-14. [S5·PM-2.5·cognitiva·1.5h] Instalar 20 términos canon SMCP RA2 sobre message markers, standard responses y NATO Phonetic mediante Word Wall categorizado y articulación phonics light cero-tolerancia.
-15. [S5·PM-2.10·cognitiva·1.0h] Descubrir y automatizar la sintaxis SMCP IMO de message markers, standard responses, NATO Phonetic y protocolo Over/Out mediante consciousness-raising y drill cero-tolerancia.
-15. [S6·PM-2.8·procedimental·2.5h] Aplicar respuestas estandarizadas SMCP y deletreo NATO Phonetic en role-play VHF con Captain Lim del MV CARIBBEAN STAR.
-16. [S6·PM-4.2·cognitiva·3.0h] Demostrar dominio integrado consolidado de Reading + Writing + Listening + Vocabulary + Grammar mediante el Cuestionario Consolidado E6 de 25 ítems con criterio PASS ≥ 70%.
-17. [S7·PM-2.6·cognitiva·1.0h] Anticipar y reconstruir órdenes y modal verbs del Berthing Tripartito mediante Predictive Listening y Dictogloss ligero.
-19. [S7·PM-2.5·cognitiva·1.5h] Consolidar 20 términos canon RA3 sobre commands a destinatarios, imperativos de seguridad y modal verbs mediante Word Wall, semantic gradients y jigsaw command-addressee.
-20. [S7·PM-2.10·cognitiva·2.0h] Consolidar commands a destinatarios, imperative, present simple Wh-questions y modals gradient con tres extensiones C05 (conditional t1, voz pasiva, presente perfecto) mediante rule formulation, transformation drills y reasoning-gap berthing.
-21. [S8·PM-2.8·procedimental·4.0h] Coordinar berthing tripartito simultáneo del MV CARIBBEAN STAR aplicando commands, imperative, modals y extensiones C05 (condicional, pasiva, presente perfecto).
-22. [S8·PM-2.9·cognitiva·1.5h] Activar las 5 funciones comunicativas canon RA3 mediante drill de function cards previo al Berthing Tripartito Simultáneo.
-23. [S9·PM-2.6·cognitiva·0.5h] Analizar y categorizar las 5 master functions IMARPOR del Role Carousel Briefing audio de Mariana, Carolina y Yurlenis.
-24. [S9·PM-2.5·cognitiva·1.0h] Cerrar Toolbelt cuádruple con 20 términos canon RA4 sobre lugares en puerto, condiciones meteo, contenedorización y maniobras mediante Word Wall categorizado y Quizlet pareo.
-25. [S9·PM-2.10·cognitiva·1.0h] Producir tag questions, present progressive con prepositional phrases y quantifiers definidos/indefinidos mediante data-based discovery, sentence building y chain story descriptiva pre-Role Carousel.
-25. [S9·PM-2.9·procedimental·3.5h] Ejecutar las 5 master functions IMARPOR mediante Role Carousel de 5 estaciones rotativas con conectores discursivos canon C06.
-28. [S10·PM-2.10·cognitiva·5.0h] Integrar las estructuras gramaticales de B1+B2+B3+B4 en un rehearsal cross-RAP del Pre-Departure Banana Reefer Compliance Check con feedback formativo cohesión gramatical no calificativo.
-29. [S11·PM-3.5·cognitiva·1.5h] Comprender el Mission Brief Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover MV CARIBBEAN STAR confirmando role assignment y rúbrica ABP capstone.
-30. [S11·PM-3.5·cognitiva·1.5h] Preparar visitor checklist + VHF script SMCP + handover pitch outline integrando vocabulario y estructuras de los 4 RAPs para el capstone.
-31. [S11·PM-3.5·procedimental·3.0h] Ensayar la jornada completa de 90 minutos cuadrilla por cuadrilla recibiendo feedback formativo NO calificativo sobre SMCP accuracy y handover fluency.
-32. [S12·PM-3.5·procedimental·3.0h] Ejecutar la jornada operacional Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover de 90 minutos por cuadrilla ante panel evaluador externo aplicando los 4 RAPs integrados.
-33. [S12·PM-3.5·actitudinal·3.0h] Reflexionar sobre el journey CEFR A1.2 → A2.1 mediante debrief panel + entrega de diplomas + ritual de cierre programa cold chain integrity.
-</t>
-        </is>
-      </c>
-      <c r="H15" s="89" t="n">
-        <v>72</v>
-      </c>
-      <c r="I15" s="89" t="n">
-        <v>28</v>
-      </c>
-      <c r="J15" s="90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evidencia de Conocimiento (E1): Comprensión lectora del Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia · Meet the Reefer Crew' (vocabulario portuario · partes del barco · oficios bananeros del cast operacional).
-Sesión: S3 · Criterio canon: ? · PM: PM-2.3
-Técnica de evaluación: Preguntas
-Instrumento: Cuestionario No 1
-Evidencia de Producto (E2): Inspection Report técnico del walk-around bay 14 MV CARIBBEAN STAR (vocabulario portuario · partes del barco · oficios bananeros · verb to be · plurales · imperative en safety commands · preposición IN para location).
-Sesión: S4 · Criterio canon: ? · PM: PM-2.4
-Técnica de evaluación: Verificación de producto
-Instrumento: Lista de verificación No 2
-Evidencia de Desempeño (E3): Comprensión auditiva SMCP · identificación de message markers, standard responses y NATO Phonetic en VHF Arrival Exchange MV CARIBBEAN STAR.
-Sesión: S5 · Criterio canon: ? · PM: PM-2.6
-Técnica de evaluación: Observación
-Instrumento: Lista de Chequeo No 3
-Evidencia de Desempeño (E4-parcial): VHF Role-Play SMCP · respuestas críticas estandarizadas y deletreo NATO Phonetic con Captain Lim Wei-Ming y Bosun Andrés Mejía (zona accuracy-cero-tolerancia).
-Sesión: S6 · Criterio canon: ? · PM: PM-2.8
-Técnica de evaluación: Observación
-Instrumento: Escala de estimación No 4
-Evidencia de Conocimiento (E6): Cuestionario Consolidado S6 · 25 ítems · 5 skills × 5 puntos (Reading + Writing + Listening + Vocabulary + Grammar) · 4-way overlap C07 RA1+RA2+RA3+RA4 · ≥70% PASS.
-Sesión: S6 · Criterio canon: ? · PM: PM-4.2
-Técnica de evaluación: Preguntas
-Instrumento: Cuestionario No 6
-Evidencia de Desempeño (E4-final): Berthing Tripartito Simultáneo del MV CARIBBEAN STAR · coordinación 5 actores aplicando 4 saberes canon RA3 + 3 extensiones C05 emergentes (zona accuracy+fluency híbrida).
-Sesión: S8 · Criterio canon: ? · PM: PM-2.8
-Técnica de evaluación: Observación
-Instrumento: Escala de estimación No 4
-Evidencia de Desempeño (E5): Producción funcional descriptiva en Role Carousel · 5 master functions IMARPOR con conectores discursivos canon en escenario banana cold chain Puerto Antioquia.
-Sesión: S9 · Criterio canon: ? · PM: PM-2.9
-Técnica de evaluación: Observación
-Instrumento: Escala de estimación No 5
-Evidencia de Desempeño (E-Misión): Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · Performance Panel MV CARIBBEAN STAR (capstone integrador 4 RAPs · 90 min/cuadrilla · panel evaluador externo 3 personas Captain Lim + Mariana + Hernando).
-Sesión: S12 · Criterio canon: ? · PM: PM-3.5
-Técnica de evaluación: Observación
-Instrumento: Rúbrica ABP capstone (6 criterios C01-C13 · 100 puntos · ≥70 PASS)
-</t>
-        </is>
-      </c>
-      <c r="K15" s="90" t="inlineStr">
-        <is>
           <t xml:space="preserve">
-• Aprendizaje colaborativo
-• Aprendizaje basado en experiencias
-• Aprendizaje basado en proyectos (ABP)
-• Trabajo colaborativo
-• Content-Based Learning
-• Task-Based Language Teaching (TBLT)
-• Juego de roles
-• Simulación
-• Aprendizaje por descubrimiento (consciousness-raising)
-• Estudio de caso</t>
+[Rationale]: APERTURA NO produce evidencias formales · criterios canon = activación afectiva + diagnóstico baseline</t>
+        </is>
+      </c>
+      <c r="G15" s="92" t="inlineStr">
+        <is>
+          <t>• #1 S1 (pm-2-1 · actitudinal · 1.0h) — Reflexionar sobre el miedo operacional al inglés VHF mediante video testimonio dramatizado de Manuel Padilla activando interés afectivo en operaciones cold chain Puerto Antioquia.
+• #2 S1 (pm-2-1 · actitudinal · 1.0h) — Reflexionar sobre el arquetipo destino cold chain coordinator mediante artefacto ICA Phytosanitary Certificate firmado por Mariana Suárez activando proyección afectiva operaciones bilingües.
+• #3 S1 (pm-2-2 · cognitiva · 1.5h) — Diagnosticar el reconocimiento léxico portuario reefer mediante galería visual diagnóstica y KWL bilingüe activando saberes operacionales previos.
+• #4 S1 (pm-2-2 · cognitiva · 1.5h) — Diagnosticar el baseline auditivo SMCP mediante audio VHF auténtico de 90 segundos y checklist binaria triangulada sin enseñar frases nuevas.</t>
+        </is>
+      </c>
+      <c r="H15" s="89" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" s="89" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J15" s="92" t="inlineStr">
+        <is>
+          <t>• (N/A — bloque APERTURA NO produce evidencias formales por diseño · rationale_sin_evidencias)</t>
+        </is>
+      </c>
+      <c r="K15" s="92" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
         </is>
       </c>
       <c r="L15" s="89" t="inlineStr">
         <is>
-          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala handover tripartita con disposición panel-cuadrilla (sesión S12 E-Misión capstone + cierre programa). Universo operacional: Puerto Antioquia · Terminal Multipropósito de Urabá · MV CARIBBEAN STAR atracado bay 14 · cluster Cavendish destino Hamburgo · ventana exportación 90 min · contenedor 25,000 USD.</t>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
         </is>
       </c>
       <c r="M15" s="89" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-• Proyector interactivo
-• Sistema de audio nítido
-• Computadores con acceso a Moodle
-• Pizarrón colaborativo
-• Mesas reorganizables (tríos · equipos de 3-6 · cuadrillas de 6)
-• Post-it amarillos · marcadores amarillos · marcadores rojos · stickers verde/amarillo/rojo
-• Carpetas personales del curso (1 por aprendiz)
-• Galería 12 imágenes etiquetadas reefer/genset/clusters/equipment portuario
-• Audio VHF auténtico 90 seg lingua franca B1 (Captain Lim Wei-Ming · Pilot Carolina · Bosun Andrés)
-• Audio Reefer Yard Walk Yurlenis Tally Clerk
-• Audio Berthing Tripartito 110 seg
-• Audio Role Carousel Briefing Mariana+Carolina+Yurlenis
-• Video testimonio dramatizado 'Manuel freezes on the VHF' (3 min)
-• ICA Phytosanitary Certificate auténtico anonimizado firmado Mariana Suárez (1 copia A4 laminada por aprendiz)
-• Story A impreso 'MV CARIBBEAN STAR Arrives at Puerto Antioquia' (5 copias por equipo)
-• Story A 'Berthing the CARIBBEAN STAR' procedural narrative + safety signage
-• Plantillas K-W-L bilingüe + Story Map + checklist binaria SMCP NATO Phonetic / Message Markers / Standard Responses
-• Word Wall Active 80 términos canon (20 RA1 + 20 RA2 SMCP + 20 RA3 + 20 RA4)
-• Cuestionario No 1 impreso (5 ítems Reading)
-• Lista de Verificación No 2 impresa (10 criterios Inspection Report)
-• Lista de Chequeo No 3 impresa (Listening SMCP)
-• Escala de Estimación No 4 impresa (Speaking VHF + Berthing)
-• Escala de Estimación No 5 impresa (Functions Role Carousel)
-• Cuestionario No 6 impreso (25 ítems Consolidado)
-• Rúbrica ABP capstone impresa (6 criterios C01-C13)
-• Function cards F1-F5 RA3 + F1-F5 master functions IMARPOR RA4
-• Sistema VHF simulado + micrófonos de diadema (1 por aprendiz · simulación VHF handset · pares por equipo)
-• Diagrama berthing maneuver tridimensional o impreso A2
-• Reefer plug demo + termómetro digital + cluster Cavendish real
-• Señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING)
-• Templates digitales visitor checklist + VHF script + handover pitch outline
-• Mission Brief impreso 'Pre-Departure Banana Reefer Compliance Check + Tripartite Handover'
-• Diplomas + pocket cards laminadas continuidad profesional
-• Foto contextual MV CARIBBEAN STAR + organigrama visual cast crew bananero (Manuel · Carolina · Mariana · Yurlenis · Hernando · Andrés · Pipa · Captain Lim Wei-Ming)</t>
+          <t>• Audio VHF auténtico 90 segundos MV CARIBBEAN STAR aproximándose al berth · lingua franca B1 entre Captain Lim Wei-Ming + bridge officer + pilot Carolina (heredado pm-1-2.B0.materiales_spark[3])
+• Banco fotográfico interno Puerto Antioquia 2025 + glosario MARPOR SENA (fuente original galería · referencia instructor)
+• Checklist binaria SMCP 3 bloques: NATO Phonetic Alphabet (26 letras Alpha-Zulu) · Message Markers (Question/Instruction/Advice/Request/Information/Warning) · Standard Responses (Affirmative/Negative/Wilco/Stand by/Read back/Say again)
+• Foto contextual MV CARIBBEAN STAR atracado en Puerto Antioquia + organigrama visual del cast crew bananero (Manuel · Carolina · Mariana · Yurlenis · Hernando · Andrés · Pipa · Captain Lim Wei-Ming) · recurso visual pre-spark para anclar el universo antes del clip
+• Galería diagnóstica 12 imágenes etiquetadas operacionales Puerto Antioquia: reefer container · reefer plug · genset · banana cluster · stem · pre-cooling chamber · plastic film bagging · Cavendish bunch · stevedore · tally clerk · refrigeration technician · bay 14 (heredado pm-1-2.B0.materiales_spark[2])
+• ICA Phytosanitary Certificate auténtico anonimizado firmado en inglés por Mariana Suárez cold chain coordinator (cluster Cavendish destino Hamburgo · ventana exportación 90 min · contenedor 25,000 USD · MV CARIBBEAN STAR bay 14) · proyección + entrega copia laminada A4 a cada aprendiz
+• Mariana Suárez en vivo (o videoconferencia) narrando en primera persona los 3 minutos críticos de firma bajo presión real un viernes 4pm · arquetipo destino encarnado para el aula
+• Maritime Phrasebook open archive + Star Reefers VHF arrival samples (≤3 años · fuente original audio · referencia instructor)
+• Plantilla KWL bilingüe simplificada · columnas K (español saberes previos) · W (inglés intuido) · L (vacía · se llena al final del programa)
+• Video testimonio dramatizado 'Manuel freezes on the VHF' (3 minutos · clip Manuel Padilla junior reefer operator congelando frente al micrófono VHF cuando Captain Lim Wei-Ming pregunta el reefer setpoint · cierre con debrief en español de Mariana Suárez · producción interna SENA + audio VHF auténtico Star Reefers Maritime Phrasebook open archive)</t>
         </is>
       </c>
       <c r="N15" s="89" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
         </is>
       </c>
       <c r="O15" s="89" t="inlineStr">
         <is>
-          <t>Programa Curso Complementario 100h (72 directas + 28 independientes · 12 sesiones × 6h) ejecutado bajo paradigma cascade v3.x heredancia tripartita: APERTURA (S1) · APROPIACIÓN (S2-S10) · TRANSFERENCIA capstone ABP (S11-S12). Universo canon banana cold chain Puerto Antioquia con cast 9 personajes (Manuel Padilla aprendiz avatar · Captain Lim Wei-Ming · Mariana Suárez · Carolina Vélez · Yurlenis Hinestroza · Pipa · Hernando Ospina · Andrés Mejía + Sergio/Diana instructores). 8 evidencias canon C01-C08 secuenciadas con anclaje matriz v1.3 explícito: E1 Reading S3 (C01·RA1) → E2 Writing S4 (C02·RA1+RA3 overlap) → E3 Listening S5 (C03·RA2) → E4-parcial Speaking S6 (C04·RA2+RA3 overlap) + E6 Cuestionario S6 (C07·4-way · checkpoint medio doble evidencia canon) → E4-final Speaking S8 (C05·RA3 berthing tripartito) → E5 Functions S9 (C06·RA3+RA4 overlap) → E-Misión S12 (C08·todos integrados · panel externo · 90 min/cuadrilla · 100% L2). 4 overlaps documentados matriz: C02 RA1+RA3 (lexical+morfosintáctica E2) · C04 RA2+RA3 (SMCP+gramática E4-parcial) · C06 RA3+RA4 (gramática+descriptiva E5) · C07 4-way (consolidación integrada E6). Densidad criterios canon máxima en RA3 (5/8 = 62.5%). Volumen saberes_conceptos máximo en RA4 (10/26 = 38.5%). S6 doble evidencia canon (E4-parcial + E6 checkpoint medio) · S10 sesión bisagra rehearsal pre-Misión sin evidencia formal. ZERO leak xlsx referencia Buenaventura: contenido 100% cascade v3.x banana cold chain · cast canon · MV CARIBBEAN STAR. Instrumentos canon estricto: Cuestionario No 1 (E1) · Lista de Verificación No 2 (E2) · Lista de Chequeo No 3 (E3) · Escala de Estimación No 4 (E4-parcial S6 + E4-final S8) · Escala de Estimación No 5 (E5) · Cuestionario No 6 (E6) · Rúbrica ABP capstone NO numerado (E-Misión). Renumeraciones heredadas literal Activity Cards: numero=15 duplicado entre PM-2.10 S5 grammar y PM-2.8 S6 speaking · numero=25 duplicado entre PM-2.10 S9 grammar y PM-2.9 S9 E5 Role Carousel · ambos preservados sin reasignar (REGLA cero invención · trazabilidad bidireccional bloqueante).</t>
-        </is>
-      </c>
-      <c r="P15" s="67" t="n"/>
-    </row>
-    <row r="16" ht="164.25" customFormat="1" customHeight="1" s="6">
-      <c r="A16" s="91" t="n"/>
-      <c r="B16" s="88" t="n"/>
-      <c r="C16" s="92" t="n"/>
-      <c r="D16" s="91" t="n"/>
-      <c r="E16" s="91" t="n"/>
-      <c r="F16" s="91" t="n"/>
-      <c r="G16" s="91" t="n"/>
-      <c r="H16" s="91" t="n"/>
-      <c r="I16" s="91" t="n"/>
-      <c r="J16" s="91" t="n"/>
-      <c r="K16" s="91" t="n"/>
-      <c r="L16" s="91" t="n"/>
-      <c r="M16" s="91" t="n"/>
-      <c r="N16" s="91" t="n"/>
-      <c r="O16" s="88" t="n"/>
-      <c r="P16" s="92" t="n"/>
-    </row>
-    <row r="17" ht="175.5" customFormat="1" customHeight="1" s="6">
-      <c r="A17" s="91" t="n"/>
-      <c r="B17" s="68" t="n"/>
-      <c r="C17" s="70" t="n"/>
-      <c r="D17" s="91" t="n"/>
-      <c r="E17" s="91" t="n"/>
-      <c r="F17" s="91" t="n"/>
-      <c r="G17" s="91" t="n"/>
-      <c r="H17" s="91" t="n"/>
-      <c r="I17" s="91" t="n"/>
-      <c r="J17" s="91" t="n"/>
-      <c r="K17" s="91" t="n"/>
-      <c r="L17" s="91" t="n"/>
-      <c r="M17" s="91" t="n"/>
-      <c r="N17" s="91" t="n"/>
-      <c r="O17" s="68" t="n"/>
-      <c r="P17" s="70" t="n"/>
+          <t>Bloque B0 · APERTURA · The Banana Reefer Welcome · Cold Chain Stand-Down &amp; Diagnostic Spark · sesiones ['S1'] · CEFR transversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="600" customFormat="1" customHeight="1" s="6">
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
+        </is>
+      </c>
+      <c r="B16" s="91" t="inlineStr">
+        <is>
+          <t>RA1</t>
+        </is>
+      </c>
+      <c r="C16" s="91" t="inlineStr"/>
+      <c r="D16" s="91" t="inlineStr">
+        <is>
+          <t>• UNIT 1: SHIP OVERVIEW
+• PARTS OF THE SHIPS
+• TYPES OF MERCHANT VESSELS
+• NAVIGATIONAL AND SAFETY-RELATED EQUIPMENT OF THE SHIP
+• REVIEW OF DEMONSTRATIVES ADJECTIVES AND VERB TO BE
+• SINGULAR AND PLURAL NOUNS
+• UNIT 2: THE CREW
+• PROFESSIONS IN PORT AND ABOARD</t>
+        </is>
+      </c>
+      <c r="E16" s="91" t="inlineStr">
+        <is>
+          <t>• IDENTIFICAR Y EXTRAER INFORMACIÓN PRECISA EN INGLÉS GENERADA EN EL INTERCAMBIO ORAL Y/O ESCRITO EN ESTE IDIOMA, DADO EN EL CUMPLIMIENTO DE LAS ACCIONES REQUERIDAS A BORDO DEL BUQUE Y EN PUERTO.
+• RECONOCER LOS DISTINTOS OFICIOS ENMARCADOS EN LOS CAMPOS MARÍTIMO Y PORTUARIO.</t>
+        </is>
+      </c>
+      <c r="F16" s="91" t="inlineStr">
+        <is>
+          <t>— SOFÍA SENA (matriz v1.3) —
+  • INTERPRETA MENSAJES SENCILLOS DE COMUNICACIÓN EN INGLÉS, SEGÚN CONTEXTO DE LAS OPERACIONES A BORDO Y EN EL PUERTO. (cara reading vocab básico)
+  • IDENTIFICA VOCABLOS BÁSICOS EN INGLÉS RELACIONADOS CON ELEMENTOS FÍSICOS DEL BUQUE Y PUERTO.
+— CANON SISTEMA C01-C08 —
+  • C01
+  • C02
+  • C07</t>
+        </is>
+      </c>
+      <c r="G16" s="91" t="inlineStr">
+        <is>
+          <t>• #7 S3 (pm-2-3 · cognitiva · 4h) — Reconocer vocabulario portuario y partes del barco en el Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia' aplicando DRTA + K-W-L + Story Map.
+• #10 S4 (pm-2-4 · procedimental · 4.5h) — Producir un Inspection Report técnico de una página sobre el walk-around del bay 14 del MV CARIBBEAN STAR aplicando vocabulario portuario y estructuras gramaticales A1.2-A1.3.
+• #5 S2 (pm-2-5 · cognitiva · 2.5h) — Mapear 20 términos canon RA1 sobre partes del barco, tipos de vessels, equipamiento y profesiones portuarias mediante Word Wall Active y mapa semántico colaborativo.
+• #8 S3 (pm-2-6 · cognitiva · 1.5h) — Reforzar comprensión auditiva del vocabulario portuario y bay counts en audio Reefer Yard Walk de Yurlenis.
+• #6 S2 (pm-2-10 · cognitiva · 2.5h) — Inducir el patrón canon de verb to be, demostrativos this/that/these/those y plurales -s/-es a partir de un corpus reefer y formular la regla en propias palabras.
+• #12 S4 (pm-4-2 · cognitiva · 1.0h) — Diseñar el banco proto de ítems Vocabulary y Reading cara RA1 del Cuestionario Consolidado E6 mediante curaduría colaborativa de 6-8 ítems sobre vocabulario portuario.</t>
+        </is>
+      </c>
+      <c r="H16" s="91" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J16" s="91" t="inlineStr">
+        <is>
+          <t>• [?] Comprensión lectora del Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia · Meet the Reefer Crew' (vocabulario portuario · partes del barco · oficios bananeros del cast operacional) · tipo=Conocimiento · instrumento=?
+• [?] Inspection Report técnico del walk-around bay 14 MV CARIBBEAN STAR (vocabulario portuario · partes del barco · oficios bananeros · verb to be · plurales · imperative en safety commands · preposición IN para location) · tipo=Producto · instrumento=?</t>
+        </is>
+      </c>
+      <c r="K16" s="91" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+        </is>
+      </c>
+      <c r="L16" s="91" t="inlineStr">
+        <is>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
+        </is>
+      </c>
+      <c r="M16" s="91" t="inlineStr">
+        <is>
+          <t>• Audio Story B B1 · Reefer Yard Walk · Yurlenis the Tally Clerk Counts the Bays (90 segundos · acento colombiano bananero)
+• Auditor's Checklist con 10 criterios visibles (verb to be · plurales con number · imperative en safety commands · preposición IN para location · 8+ términos Word Wall · cobertura partes barco · cobertura oficios · cohesión párrafos · formato plantilla · ortografía controlada)
+• Banco fotográfico Puerto Antioquia 2025 silueta MV CARIBBEAN STAR seccionada para anclaje deíctico this/that/these/those
+• Banco fotográfico operacional Puerto Antioquia 2025 (silueta MV CARIBBEAN STAR seccionada + 20 imágenes una por término · heredado de pm-1-2.B1.key_vocabulary_per_rap)
+• Catálogo 20 key terms canon RA1 con definición operacional banana cold chain (ship · hull · bow · stern · bridge · cargo holds · reefer plugs · genset · stevedore · tally clerk · pilot · bosun · refrigeration technician · cold chain coordinator · safety manager · cluster · bay · setpoint · pre-cooling · phytosanitary)
+• Corpus canon 12 oraciones contextualizadas bay 14 MV CARIBBEAN STAR (verb to be + demostrativos + plurales + there is/are + articles · heredado literal de pm-1-2.B1.grammar_items_per_rap)
+• Ejemplo modelo Inspection Report ya completado por Mariana (cold chain coordinator) sobre bay 12 del MV PACIFIC GREEN (mentor text genre analysis · 1 página A1.2-A1.3 · 4 recursos lingüísticos visibles)
+• Forvo audio nativo pronunciación 20 términos canon RA1 (referencia phonics para hispanohablantes)
+• Forvo audio nativo pronunciación plurales -s/-es críticos (clusters /klʌstərz/ · containers /kənˈteɪnərz/ · stevedores /ˈstiːvədɔːrz/) y stress en cifras numéricas
+• Foto referencial MV CARIBBEAN STAR + mapa Puerto Antioquia + organigrama crew bananero (recurso visual pre-reading DRTA · activación de esquemas)
+• Glosario portuario A1.2 con los 15 términos vocab_extraible canon RA1 (reefer ship · hull · bow · stern · bridge · cargo holds · reefer plugs · containers · stevedore · pilot · bosun · tally clerk · refrigeration technician · cold chain coordinator · genset)
+• Glosario portuario A1.2 con los 20 términos canon RA1 + 4 imperative verbs canónicos del walk-around (Check · Verify · Inspect · Report)
+• Guía Principio de Tres Versiones PM-4.2 (parecido pero diferente · nuevo personaje · nuevo bay count · nuevo merchant vessel · mismo nivel CEFR A1.2)
+• Plantilla Inspection Report MV CARIBBEAN STAR bay 14 (template real banana cold chain · campos: Vessel Name · Berth Number · Date of Inspection · Bay Inspected · Vessel Parts Checked · Containers Identified · Reefer Plugs Status · Genset Setpoint · Cold Chain Team On Duty · Safety Commands Issued · Final Status)
+• Plantilla Item Bank Cara RA1 con 8 slots diferenciados en Vocabulary RA1 (multiple choice + matching) y Reading RA1 (true/false/not given + short answer)
+• Quizlet set 20 términos RA1 banana cold chain · matching y flashcards modo pre-exposición receptiva
+• Story A Reading: 'MV CARIBBEAN STAR Arrives at Puerto Antioquia · Meet the Reefer Crew' (texto fundacional 205 palabras A1.2 · narrativa descriptiva técnica adaptada de Star Reefers Vessel Profiles + IMO STCW crew nomenclature)
+• Transcript referencial bilingüe del audio (entregado al instructor · NO al aprendiz)</t>
+        </is>
+      </c>
+      <c r="N16" s="91" t="inlineStr">
+        <is>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
+        </is>
+      </c>
+      <c r="O16" s="91" t="inlineStr">
+        <is>
+          <t>Bloque B1 · APROPIACION · The Reefer Crew · Recognizing Ships, Parts &amp; Port Professions · sesiones ['S2', 'S3', 'S4'] · CEFR A1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="600" customFormat="1" customHeight="1" s="6">
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
+        </is>
+      </c>
+      <c r="B17" s="91" t="inlineStr">
+        <is>
+          <t>RA2</t>
+        </is>
+      </c>
+      <c r="C17" s="91" t="inlineStr"/>
+      <c r="D17" s="91" t="inlineStr">
+        <is>
+          <t>• UNIT 5: INTRODUCING IMO STANDARD MARINE COMMUNICATION PHRASES (SMCP)
+• STANDARD SPELLING
+• MESSAGE MARKERS
+• STANDARD RESPONSES AND ORGANIZATIONAL PHRASES</t>
+        </is>
+      </c>
+      <c r="E17" s="91" t="inlineStr">
+        <is>
+          <t>• RECONOCER LA MANERA DE DELETREAR LOS VOCABLOS EN INGLÉS.
+• RESPONDER EN INGLÉS EN CONVERSACIONES SENCILLAS Y UTILIZANDO LAS FRASES ESTANDARIZADAS POR LA OMI, EN EL DESEMPEÑO DE LAS OPERACIONES QUE SE GENEREN EN EL CONTEXTO.
+• IDENTIFICAR VOCABULARIO COMÚN EN INGLÉS, EN LAS FRASES ESTANDARIZADAS DE LA OMI PARA LA COMUNICACIÓN MARÍTIMA.</t>
+        </is>
+      </c>
+      <c r="F17" s="91" t="inlineStr">
+        <is>
+          <t>— SOFÍA SENA (matriz v1.3) —
+  • INTERPRETA MENSAJES SENCILLOS DE COMUNICACIÓN EN INGLÉS, SEGÚN CONTEXTO DE LAS OPERACIONES A BORDO Y EN EL PUERTO. (cara SMCP listening)
+  • RESPONDE EN INGLÉS EN CONVERSACIONES SENCILLAS UTILIZANDO LAS FRASES ESTANDARIZADAS POR LA OMI.
+— CANON SISTEMA C01-C08 —
+  • C03
+  • C04
+  • C07</t>
+        </is>
+      </c>
+      <c r="G17" s="91" t="inlineStr">
+        <is>
+          <t>• #14 S5 (pm-2-5 · cognitiva · 1.5h) — Instalar 20 términos canon SMCP RA2 sobre message markers, standard responses y NATO Phonetic mediante Word Wall categorizado y articulación phonics light cero-tolerancia.
+• #13 S5 (pm-2-6 · procedimental · 3.0h) — Identificar mensajes correctos y distractores SMCP en audio VHF auténtico de Captain Lim Wei-Ming según protocolo OMI.
+• #15 S6 (pm-2-8 · procedimental · 2.5h) — Aplicar respuestas estandarizadas SMCP y deletreo NATO Phonetic en role-play VHF con Captain Lim del MV CARIBBEAN STAR.
+• #15 S5 (pm-2-10 · cognitiva · 1.0h) — Descubrir y automatizar la sintaxis SMCP IMO de message markers, standard responses, NATO Phonetic y protocolo Over/Out mediante consciousness-raising y drill cero-tolerancia.
+• #16 S6 (pm-4-2 · cognitiva · 3.0h) — Demostrar dominio integrado consolidado de Reading + Writing + Listening + Vocabulary + Grammar mediante el Cuestionario Consolidado E6 de 25 ítems con criterio PASS ≥ 70%.</t>
+        </is>
+      </c>
+      <c r="H17" s="91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I17" s="91" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J17" s="91" t="inlineStr">
+        <is>
+          <t>• [?] Comprensión auditiva SMCP · identificación de message markers, standard responses y NATO Phonetic en VHF Arrival Exchange MV CARIBBEAN STAR · tipo=Desempeño · instrumento=?
+• [?] VHF Role-Play SMCP · respuestas críticas estandarizadas y deletreo NATO Phonetic con Captain Lim Wei-Ming y Bosun Andrés Mejía (zona accuracy-cero-tolerancia) · tipo=Desempeño · instrumento=?
+• [?] Cuestionario Consolidado S6 · 25 ítems · 5 skills × 5 puntos (Reading + Writing + Listening + Vocabulary + Grammar) · 4-way overlap C07 RA1+RA2+RA3+RA4 · ≥70% PASS · tipo=Conocimiento · instrumento=?</t>
+        </is>
+      </c>
+      <c r="K17" s="91" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+        </is>
+      </c>
+      <c r="L17" s="91" t="inlineStr">
+        <is>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
+        </is>
+      </c>
+      <c r="M17" s="91" t="inlineStr">
+        <is>
+          <t>• Audio Captain Lim Wei-Ming Story B 105 segundos lingua franca B1+ Singapore + Pilot Carolina + Bosun Andrés (referencia auténtica para corpus consciousness-raising)
+• Audio Story B B2 · MV CARIBBEAN STAR Arrival · Live VHF Exchange with Captain Lim Wei-Ming (105 segundos · lingua franca B1+ Singapore + Pilot B2 colombiana + Bosun B1 Turbo)
+• Audio Story B Listening 'MV CARIBBEAN STAR Arrival · Live VHF Exchange with Captain Lim Wei-Ming' (105 segundos · ya conocido de S5 · usado para shadowing pre-task)
+• Audio voicemail SMCP Captain Lim Wei-Ming nuevo (paralelo al Story B Listening de S5 · TTS pausado 0.85x · ≈90 segundos · uso Sección 3)
+• Cuestionario Consolidado E6 ensamblado PM-4.2 v3.0 · 25 ítems · 5 secciones × 5 puntos · Reading + Writing + Listening + Vocabulary + Grammar · Principio de Tres Versiones · ≥70% PASS · checkpoint medio programa
+• Forvo audio nativo NATO Phonetic Alphabet completa (Charlie/Sierra/Tango stress canon) y standard responses críticos (Wilco/Roger/Affirmative/Negative/Standby)
+• Forvo audio nativo pronunciación NATO Phonetic Alphabet completa (Alpha-Zulu) y standard responses críticos (Roger · Wilco · Affirmative · Negative · Standby)
+• IMO SMCP 2002 Standard Marine Communication Phrases (referencia oficial OMI)
+• Quizlet set 20 términos SMCP RA2 · matching message marker-categoría · flashcards spell-out NATO Phonetic
+• Tabla 8 Message Markers SMCP IMO + 5 Standard Responses con definición operacional y stress fonológico marcado para hispanohablantes
+• Tabla NATO Phonetic Alphabet aplicada a call signs banana reefer
+• Tabla NATO Phonetic Alphabet completa (Alpha · Bravo · Charlie · Delta · Echo · Foxtrot · Golf · Hotel · India · Juliet · Kilo · Lima · Mike · November · Oscar · Papa · Quebec · Romeo · Sierra · Tango · Uniform · Victor · Whiskey · X-ray · Yankee · Zulu)
+• Tabla canon IMO SMCP 2002 message markers + standard responses + NATO Phonetic Alphabet + protocolo Over/Out (heredado de pm-1-2.B2.grammar_items_per_rap)
+• Tabla canon IMO Standard Marine Communication Phrases 2002 · 8 message markers + 5 standard responses + NATO Phonetic Alphabet completa (heredado de pm-1-2.B2.key_vocabulary_per_rap)
+• Tabla scaffolding inventario container para Sección 5 Grammar HOTS (datos input + formula proporcionada para sentence construction)
+• Texto paralelo Reading cara RA1 con personaje Laura del cast bananero (≈220 palabras A1.2 · scenario alterno banana cold chain · uso Sección 1)</t>
+        </is>
+      </c>
+      <c r="N17" s="91" t="inlineStr">
+        <is>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
+        </is>
+      </c>
+      <c r="O17" s="91" t="inlineStr">
+        <is>
+          <t>Bloque B2 · APROPIACION · The VHF Voice · Comprehending IMO Standard Marine Communication Phrases · sesiones ['S5', 'S6'] · CEFR A1.3</t>
+        </is>
+      </c>
       <c r="U17" s="7" t="n"/>
     </row>
-    <row r="18" ht="49.5" customFormat="1" customHeight="1" s="6">
-      <c r="A18" s="91" t="n"/>
+    <row r="18" ht="600" customFormat="1" customHeight="1" s="6">
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
+        </is>
+      </c>
       <c r="B18" s="93" t="inlineStr">
         <is>
-          <t>RA2 COMPRENDER VOCABLOS PRINCIPALES DE LAS FRASES ESTANDARIZADAS POR LA OMI, EN INGLÉS, PARA INICIAR LA INTERACCIÓN POR MEDIO ESCRITO Y ORAL, DE ACUERDO CON LOS ROLES DESCRITOS DENTRO DE LA INDUSTRIA MARÍTIMA Y PORTUARIA.</t>
-        </is>
-      </c>
-      <c r="C18" s="92" t="n"/>
-      <c r="D18" s="91" t="n"/>
-      <c r="E18" s="91" t="n"/>
-      <c r="F18" s="91" t="n"/>
-      <c r="G18" s="91" t="n"/>
-      <c r="H18" s="91" t="n"/>
-      <c r="I18" s="91" t="n"/>
-      <c r="J18" s="91" t="n"/>
-      <c r="K18" s="91" t="n"/>
-      <c r="L18" s="91" t="n"/>
-      <c r="M18" s="91" t="n"/>
-      <c r="N18" s="91" t="n"/>
-      <c r="O18" s="33" t="n"/>
-      <c r="P18" s="67" t="n"/>
-    </row>
-    <row r="19" ht="290.25" customFormat="1" customHeight="1" s="6">
-      <c r="A19" s="91" t="n"/>
-      <c r="B19" s="88" t="n"/>
-      <c r="C19" s="92" t="n"/>
-      <c r="D19" s="91" t="n"/>
-      <c r="E19" s="91" t="n"/>
-      <c r="F19" s="91" t="n"/>
-      <c r="G19" s="91" t="n"/>
-      <c r="H19" s="91" t="n"/>
-      <c r="I19" s="91" t="n"/>
-      <c r="J19" s="91" t="n"/>
-      <c r="K19" s="91" t="n"/>
-      <c r="L19" s="91" t="n"/>
-      <c r="M19" s="91" t="n"/>
-      <c r="N19" s="91" t="n"/>
-      <c r="O19" s="68" t="n"/>
-      <c r="P19" s="70" t="n"/>
-    </row>
-    <row r="20" ht="227.25" customFormat="1" customHeight="1" s="6">
-      <c r="A20" s="91" t="n"/>
+          <t>RA3</t>
+        </is>
+      </c>
+      <c r="C18" s="91" t="inlineStr"/>
+      <c r="D18" s="91" t="inlineStr">
+        <is>
+          <t>• COMMANDS (TO: OFFICERS, SAILORS, HELMSMAN, CAPTAINS, ENGINEERS, STEWARD, CRANE OPERATORS)
+• REVIEW OF PRESENT SIMPLE TENSE
+• IMPERATIVE
+• MODAL VERBS: CAN, COULD, SHOULD, MUST FOR REQUEST, PROHIBITION, POSSIBILITY, PERMISSION</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>• IDENTIFICAR ESTRUCTURAS GRAMATICALES BÁSICAS EN INGLÉS, TALES COMO VERBOS RELACIONADOS CON LAS ACCIONES EMPRENDIDAS DENTRO DE LOS OFICIOS A BORDO DEL BUQUE Y EN PUERTO.
+• EXPRESAR E INTERPRETAR ÓRDENES QUE SE DAN EN EL CUMPLIMIENTO DE LAS DISTINTAS FUNCIONES REQUERIDAS EN EL EJERCICIO DE LOS ROLES A BORDO DEL BUQUE Y EN PUERTO.
+• EXPRESAR PROHIBICIÓN, PERMISIÓN, POSIBILIDAD O HACER PEDIDOS EN INGLÉS, EN CUANTO A PROCESOS ENMARCADOS EN EL DESEMPEÑO DE LAS OPERACIONES MARÍTIMAS Y PORTUARIAS.</t>
+        </is>
+      </c>
+      <c r="F18" s="91" t="inlineStr">
+        <is>
+          <t>— SOFÍA SENA (matriz v1.3) —
+  • RESPONDE EN INGLÉS CON INFORMACIÓN PERTINENTE A COMANDOS E INTERCAMBIOS SENCILLOS (cara comandos/imperativo)
+  • APLICA REGLAS GRAMATICALES BÁSICAS EN INGLÉS PARA COMUNICACIÓN PUERTO-BUQUE.
+— CANON SISTEMA C01-C08 —
+  • C02
+  • C04
+  • C05
+  • C06
+  • C07</t>
+        </is>
+      </c>
+      <c r="G18" s="91" t="inlineStr">
+        <is>
+          <t>• #19 S7 (pm-2-5 · cognitiva · 1.5h) — Consolidar 20 términos canon RA3 sobre commands a destinatarios, imperativos de seguridad y modal verbs mediante Word Wall, semantic gradients y jigsaw command-addressee.
+• #17 S7 (pm-2-6 · cognitiva · 1.0h) — Anticipar y reconstruir órdenes y modal verbs del Berthing Tripartito mediante Predictive Listening y Dictogloss ligero.
+• #21 S8 (pm-2-8 · procedimental · 4.0h) — Coordinar berthing tripartito simultáneo del MV CARIBBEAN STAR aplicando commands, imperative, modals y extensiones C05 (condicional, pasiva, presente perfecto).
+• #22 S8 (pm-2-9 · cognitiva · 1.5h) — Activar las 5 funciones comunicativas canon RA3 mediante drill de function cards previo al Berthing Tripartito Simultáneo.
+• #20 S7 (pm-2-10 · cognitiva · 2.0h) — Consolidar commands a destinatarios, imperative, present simple Wh-questions y modals gradient con tres extensiones C05 (conditional t1, voz pasiva, presente perfecto) mediante rule formulation, transformation drills y reasoning-gap berthing.</t>
+        </is>
+      </c>
+      <c r="H18" s="91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J18" s="91" t="inlineStr">
+        <is>
+          <t>• [?] Berthing Tripartito Simultáneo del MV CARIBBEAN STAR · coordinación 5 actores aplicando 4 saberes canon RA3 + 3 extensiones C05 emergentes (zona accuracy+fluency híbrida) · tipo=Desempeño · instrumento=?</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
+        <is>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
+        </is>
+      </c>
+      <c r="M18" s="91" t="inlineStr">
+        <is>
+          <t>• Audio Story B B3 · Berthing Tripartito · Pilot, Captain Lim, Bosun &amp; Pipa Coordinate Live (110 segundos · multi-actor procedural A2.0)
+• Audio Story B Berthing Tripartito 110 segundos Pilot+Captain Lim+Bosun+Pipa (referencia auténtica para reasoning-gap)
+• Audio Story B Listening 'Berthing Tripartito · Pilot, Captain Lim, Bosun &amp; Pipa Coordinate Live' (110 segundos · ya conocido de S7 · usado para shadowing pre-task de las 3 extensiones C05 emergentes)
+• Corpus canon 7 estructuras RA3 (4 canon + 3 extensiones C05) con ejemplos contextualizados berthing tripartito (heredado literal de pm-1-2.B3.grammar_items_per_rap)
+• Diagrama berthing maneuver Puerto Antioquia berth tres
+• Diagrama operacional MV CARIBBEAN STAR berthing aproximación a berth tres con etiquetas siete destinatarios canon (Officers · Sailors · Helmsman · Captains · Engineers · Steward · Crane Operators) heredado de pm-1-2.B3.key_vocabulary_per_rap
+• Function cards F1-F5 RA3 heredadas de PM-2.9 S8 warm-up (commands a destinatarios · safety imperatives · Wh-questions present simple · modals · coordinación tripartita conditional+pasiva+presente perfecto)
+• Guía operativa bilingüe Berthing Tripartito MV CARIBBEAN STAR (referencia de actores canon Pilot Carolina, Captain Lim, Bosun Andrés, Pipa)
+• Manual operacional bananero reefer Star Reefers + protocolo PPE Puerto Antioquia 2025 (referencia instructor para imperatives safety)
+• Mapa visual 5 actores berthing + procedural narrative Story A Reading 215 palabras (referencia espacial reasoning-gap)
+• Quizlet set 20 términos RA3 commands and modals · matching command-addressee · flashcards modal gradient
+• Story A Reading 'Berthing the CARIBBEAN STAR · Commands, Imperatives and Modals on the Pier' (215 palabras A2.0 · ya conocido de S7 · referencia procedural)
+• Tabla referencial de las 5 funciones canon RA3 con exponentes validados en pm-1-2 (F1 commands · F2 imperatives · F3 Wh-questions · F4 modales · F5 extensiones C05)
+• Tabla resumen 4 saberes canon RA3 (commands · imperative · present simple Wh-questions · modal verbs) + 3 extensiones C05 emergentes (conditional tipo 1 · voz pasiva · presente perfecto) con patrón canónico y ejemplos contextualizados berthing</t>
+        </is>
+      </c>
+      <c r="N18" s="91" t="inlineStr">
+        <is>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
+        </is>
+      </c>
+      <c r="O18" s="89" t="inlineStr">
+        <is>
+          <t>Bloque B3 · APROPIACION · The Bridge-to-Yard Bridge · Applying Operational Grammar Port-to-Ship · sesiones ['S7', 'S8'] · CEFR A2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="600" customFormat="1" customHeight="1" s="6">
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
+        </is>
+      </c>
+      <c r="B19" s="91" t="inlineStr">
+        <is>
+          <t>RA4</t>
+        </is>
+      </c>
+      <c r="C19" s="91" t="inlineStr"/>
+      <c r="D19" s="91" t="inlineStr">
+        <is>
+          <t>• UNIT 3: PLACES IN PORT AND POSITION
+• PLACES IN PORT · LOCATIONS
+• WEATHER CONDITIONS
+• TAG QUESTIONS
+• REVIEW OF PRESENT PROGRESSIVE AND PREPOSITIONAL PHRASES OF GEOGRAPHIC LOCATION AND DISTANCE
+• UNIT 4: IN PORT
+• CONTAINERIZATION
+• PACKING, SHIPPING AND CARGO HANDLING
+• MANEUVERING (MOORING, DOCKING, DEPARTURE)
+• QUANTIFIERS</t>
+        </is>
+      </c>
+      <c r="E19" s="91" t="inlineStr">
+        <is>
+          <t>• HABLAR SOBRE UBICACIONES EN INGLÉS QUE PERMITAN AL INTERLOCUTOR CONOCER EL ESPACIO FÍSICO EN EL QUE SE DESEMPEÑAN LAS FUNCIONES A BORDO DEL BUQUE.
+• DESCRIBIR ELEMENTOS Y PROCESOS EN INGLÉS, DERIVADOS DE LOS DISTINTOS ROLES QUE SE EJERCEN EN EL CUMPLIMIENTO DE LAS OBLIGACIONES A BORDO DEL BUQUE Y EN PUERTO.</t>
+        </is>
+      </c>
+      <c r="F19" s="91" t="inlineStr">
+        <is>
+          <t>— SOFÍA SENA (matriz v1.3) —
+  • DESCRIBE EN INGLÉS PROCESOS Y FUNCIONES PROPIAS DEL CONTEXTO MARÍTIMO Y PORTUARIO.
+— CANON SISTEMA C01-C08 —
+  • C06
+  • C07</t>
+        </is>
+      </c>
+      <c r="G19" s="91" t="inlineStr">
+        <is>
+          <t>• #24 S9 (pm-2-5 · cognitiva · 1.0h) — Cerrar Toolbelt cuádruple con 20 términos canon RA4 sobre lugares en puerto, condiciones meteo, contenedorización y maniobras mediante Word Wall categorizado y Quizlet pareo.
+• #23 S9 (pm-2-6 · cognitiva · 0.5h) — Analizar y categorizar las 5 master functions IMARPOR del Role Carousel Briefing audio de Mariana, Carolina y Yurlenis.
+• #25 S9 (pm-2-9 · procedimental · 3.5h) — Ejecutar las 5 master functions IMARPOR mediante Role Carousel de 5 estaciones rotativas con conectores discursivos canon C06.
+• #25 S9 (pm-2-10 · cognitiva · 1.0h) — Producir tag questions, present progressive con prepositional phrases y quantifiers definidos/indefinidos mediante data-based discovery, sentence building y chain story descriptiva pre-Role Carousel.
+• #28 S10 (pm-2-10 · cognitiva · 5.0h) — Integrar las estructuras gramaticales de B1+B2+B3+B4 en un rehearsal cross-RAP del Pre-Departure Banana Reefer Compliance Check con feedback formativo cohesión gramatical no calificativo.</t>
+        </is>
+      </c>
+      <c r="H19" s="91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="91" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J19" s="91" t="inlineStr">
+        <is>
+          <t>• [?] Producción funcional descriptiva en Role Carousel · 5 master functions IMARPOR con conectores discursivos canon en escenario banana cold chain Puerto Antioquia · tipo=Desempeño · instrumento=?</t>
+        </is>
+      </c>
+      <c r="K19" s="91" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+        </is>
+      </c>
+      <c r="L19" s="91" t="inlineStr">
+        <is>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
+        </is>
+      </c>
+      <c r="M19" s="91" t="inlineStr">
+        <is>
+          <t>• Audio Story B B4 · Role Carousel Briefing · Mariana, Carolina &amp; Yurlenis Describe Their Functions (100 segundos · A2.0-A2.1)
+• Audio Story B Role Carousel Briefing 100 segundos Mariana+Carolina+Yurlenis (referencia auténtica entonación tag questions rising/falling)
+• Corpus canon 8 intercambios contextualizados handover Mariana-Carolina bay 14 (tag questions + present progressive prepositional + quantifiers + conectores · heredado literal de pm-1-2.B4.grammar_items_per_rap)
+• Escenario Pre-Departure Banana Reefer Compliance Check 4 fases con script-skeleton operacional (heredado de pm-1-2.B4.rehearsal_pre_mision_S10)
+• Forvo audio nativo entonación tag questions afirmativas-negativas y stress en quantifiers numéricos (forty-seven · twenty-seven · two)
+• Forvo audio nativo pronunciación quantifiers numéricos y prepositional phrases de distancia (forty-seven · twenty-seven tonnes · two nautical miles · seventy-five percent · thirteen point three degrees)
+• Guía feedback formativo cohesión gramatical 7 checks NO calificativos (canon REGLA v3.0 PM-2.10 rehearsal S10)
+• Guía operativa bilingüe Universo Banana Cold Chain Puerto Antioquia (referencia de actores canon Carolina, Mariana, Yurlenis y vocabulario contextualizado)
+• Mapa satelital Puerto Antioquia 2025 con etiquetas lugares clave (deep-water terminal · reefer yard · pre-cooling chamber · pier · berth tres) heredado de pm-1-2.B4.key_vocabulary_per_rap
+• Quizlet set 20 términos RA4 places maneuvering quantifiers + Quizlet set consolidado 80 términos Toolbelt cuádruple cross-RAP RA1+RA2+RA3+RA4
+• Tabla canon 18 estructuras gramaticales programa (B1 5 + B2 5 + B3 7 + B4 5 incluyendo extensiones C05 y C06 marcadas) consolidada cross-RAP (heredada literal de pm-1-2.sub_bloques_tripartitos[1-4].grammar_items_per_rap)
+• Tabla canon Sergio post-Wave 1 de las 5 master functions IMARPOR (F1 roles &amp; chain of command · F2 maneuvers · F3 weather · F4 cargo &amp; quantification · F5 handover tag questions)
+• Tabla referencial de 6 conectores discursivos canon C06 con ejemplos contextualizados (and · but · or · because · so · although)
+• Tabla referencial de las 5 master functions IMARPOR (canon Sergio post-Wave 1)</t>
+        </is>
+      </c>
+      <c r="N19" s="91" t="inlineStr">
+        <is>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
+        </is>
+      </c>
+      <c r="O19" s="91" t="inlineStr">
+        <is>
+          <t>Bloque B4 · APROPIACION · The Cold Chain Storyteller · Describing Places, Operations &amp; Roles · sesiones ['S9', 'S10'] · CEFR A2.0-A2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="600" customFormat="1" customHeight="1" s="6">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
+        </is>
+      </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>RA3 APLICAR LAS REGLAS GRAMATICALES BÁSICAS DEL IDIOMA INGLÉS QUE GARANTICEN LA COMUNICACIÓN SENCILLA DE PUERTO A BUQUE Y VICEVERSA, SEGÚN LAS NECESIDADES ORIGINADAS EN EL DESARROLLO DE LAS OPERACIONES MARÍTIMAS Y PORTUARIAS.</t>
-        </is>
-      </c>
-      <c r="C20" s="67" t="n"/>
-      <c r="D20" s="91" t="n"/>
-      <c r="E20" s="91" t="n"/>
-      <c r="F20" s="91" t="n"/>
-      <c r="G20" s="91" t="n"/>
-      <c r="H20" s="91" t="n"/>
-      <c r="I20" s="91" t="n"/>
-      <c r="J20" s="91" t="n"/>
-      <c r="K20" s="91" t="n"/>
-      <c r="L20" s="91" t="n"/>
-      <c r="M20" s="91" t="n"/>
-      <c r="N20" s="91" t="n"/>
-      <c r="O20" s="33" t="n"/>
-      <c r="P20" s="72" t="n"/>
+          <t>transversal_capstone
+Transferencia capstone · integra RA1+RA2+RA3+RA4 vía Misión ABP (Pre-Departure Banana Reefer Compliance Check) · NO cubre nuevo RAP</t>
+        </is>
+      </c>
+      <c r="C20" s="91" t="inlineStr"/>
+      <c r="D20" s="91" t="inlineStr">
+        <is>
+          <t>• (N/A — bloque TRANSFERENCIA capstone: integra y transfiere saberes ya cubiertos en B1-B4 · NO introduce saberes nuevos · cobertura via Misión ABP)</t>
+        </is>
+      </c>
+      <c r="E20" s="91" t="inlineStr">
+        <is>
+          <t>• [Movilizado de RA1] IDENTIFICAR Y EXTRAER INFORMACIÓN PRECISA EN INGLÉS GENERADA EN EL INTERCAMBIO ORAL Y/O ESCRITO EN ESTE IDIOMA, DADO EN EL CUMPLIMIENTO DE LAS ACCIONES REQUERIDAS A BORDO DEL BUQUE Y EN PUERTO.
+• [Movilizado de RA1] RECONOCER LOS DISTINTOS OFICIOS ENMARCADOS EN LOS CAMPOS MARÍTIMO Y PORTUARIO.
+• [Movilizado de RA2] RECONOCER LA MANERA DE DELETREAR LOS VOCABLOS EN INGLÉS.
+• [Movilizado de RA2] RESPONDER EN INGLÉS EN CONVERSACIONES SENCILLAS Y UTILIZANDO LAS FRASES ESTANDARIZADAS POR LA OMI, EN EL DESEMPEÑO DE LAS OPERACIONES QUE SE GENEREN EN EL CONTEXTO.
+• [Movilizado de RA2] IDENTIFICAR VOCABULARIO COMÚN EN INGLÉS, EN LAS FRASES ESTANDARIZADAS DE LA OMI PARA LA COMUNICACIÓN MARÍTIMA.
+• [Movilizado de RA3] IDENTIFICAR ESTRUCTURAS GRAMATICALES BÁSICAS EN INGLÉS, TALES COMO VERBOS RELACIONADOS CON LAS ACCIONES EMPRENDIDAS DENTRO DE LOS OFICIOS A BORDO DEL BUQUE Y EN PUERTO.
+• [Movilizado de RA3] EXPRESAR E INTERPRETAR ÓRDENES QUE SE DAN EN EL CUMPLIMIENTO DE LAS DISTINTAS FUNCIONES REQUERIDAS EN EL EJERCICIO DE LOS ROLES A BORDO DEL BUQUE Y EN PUERTO.
+• [Movilizado de RA3] EXPRESAR PROHIBICIÓN, PERMISIÓN, POSIBILIDAD O HACER PEDIDOS EN INGLÉS, EN CUANTO A PROCESOS ENMARCADOS EN EL DESEMPEÑO DE LAS OPERACIONES MARÍTIMAS Y PORTUARIAS.
+• [Movilizado de RA4] HABLAR SOBRE UBICACIONES EN INGLÉS QUE PERMITAN AL INTERLOCUTOR CONOCER EL ESPACIO FÍSICO EN EL QUE SE DESEMPEÑAN LAS FUNCIONES A BORDO DEL BUQUE.
+• [Movilizado de RA4] DESCRIBIR ELEMENTOS Y PROCESOS EN INGLÉS, DERIVADOS DE LOS DISTINTOS ROLES QUE SE EJERCEN EN EL CUMPLIMIENTO DE LAS OBLIGACIONES A BORDO DEL BUQUE Y EN PUERTO.</t>
+        </is>
+      </c>
+      <c r="F20" s="91" t="inlineStr">
+        <is>
+          <t>— SOFÍA SENA (matriz v1.3) —
+  • (integra los 7 criterios SOFÍA cubiertos en B1-B4 vía evidencia E-Misión ABP)
+— CANON SISTEMA C01-C08 —
+  • C08</t>
+        </is>
+      </c>
+      <c r="G20" s="91" t="inlineStr">
+        <is>
+          <t>• #29 S11 (pm-3-5 · cognitiva · 1.5h) — Comprender el Mission Brief Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover MV CARIBBEAN STAR confirmando role assignment y rúbrica ABP capstone.
+• #30 S11 (pm-3-5 · cognitiva · 1.5h) — Preparar visitor checklist + VHF script SMCP + handover pitch outline integrando vocabulario y estructuras de los 4 RAPs para el capstone.
+• #31 S11 (pm-3-5 · procedimental · 3.0h) — Ensayar la jornada completa de 90 minutos cuadrilla por cuadrilla recibiendo feedback formativo NO calificativo sobre SMCP accuracy y handover fluency.
+• #32 S12 (pm-3-5 · procedimental · 3.0h) — Ejecutar la jornada operacional Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover de 90 minutos por cuadrilla ante panel evaluador externo aplicando los 4 RAPs integrados.
+• #33 S12 (pm-3-5 · actitudinal · 3.0h) — Reflexionar sobre el journey CEFR A1.2 → A2.1 mediante debrief panel + entrega de diplomas + ritual de cierre programa cold chain integrity.</t>
+        </is>
+      </c>
+      <c r="H20" s="91" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J20" s="91" t="inlineStr">
+        <is>
+          <t>• [?] Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · Performance Panel MV CARIBBEAN STAR (capstone integrador 4 RAPs · 90 min/cuadrilla · panel evaluador externo 3 personas Captain Lim + Mariana + Hernando) · tipo=Desempeño · instrumento=?</t>
+        </is>
+      </c>
+      <c r="K20" s="91" t="inlineStr">
+        <is>
+          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+        </is>
+      </c>
+      <c r="L20" s="91" t="inlineStr">
+        <is>
+          <t>Ambiente formativo multimodal con 3 configuraciones según tipo de actividad: (1) AULA REGULAR con proyector interactivo + sistema de audio + computadores con acceso a Moodle + mesas reorganizables para tríos / equipos de 3-6 / cuadrillas de 6 aprendices + pizarrón colaborativo (sesiones APERTURA S1 + scaffolds APROPIACIÓN vocab/grammar/reading S2/S4/S5/S7/S9 + ejecución E1/E2/E3/E6 S3/S4/S5/S6 + briefing/preparación BT S11). (2) AMBIENTE PLURITECNOLÓGICO SIMULADO con sistema VHF + micrófonos de diadema dobles por equipo + sala handover meeting con mesa tripartita + diagrama berthing tridimensional (sesiones E4-parcial S6 + E4-final S8 berthing tripartito + E5 Role Carousel S9 + rehearsal S10/S11). (3) AMBIENTE PLURITECNOLÓGICO INDUSTRIAL COMPLETO reefer yard operativo con plug + genset + bays simuladas + cluster Cavendish real + termómetro digital + señalética bilingüe pier (NO SMOKING · COLD CHAIN ZONE · MUSTER STATION · GENSET WARNING) + sistema VHF operativo + bridge simulado + sala</t>
+        </is>
+      </c>
+      <c r="M20" s="91" t="inlineStr">
+        <is>
+          <t>• Bitácora feedback panel triangulado (template registro descriptores cualitativos por cuadrilla · NO sumativo sino mapa continuidad profesional)
+• Bitácora rehearsal feedback formativo (template registro 3 errores + 3 aciertos por cuadrilla observada · uso individual cross-cuadrilla)
+• Cluster Cavendish real con plastic film bagging + sello GlobalGAP/Rainforest Alliance (asset físico usado en rehearsal cold chain integrity)
+• ICA Phytosanitary Certificate template (formato real anonimizado · campos en inglés · base para handover pitch + Q&amp;A)
+• Línea de tiempo visual journey programa CEFR A1.2 → A2.1 (hitos canon: S1 spark Manuel + S3 E1 + S6 E4-parcial+E6 + S8 E4-final + S9 E5 + S12 E-Misión capstone)
+• Mapa Puerto Antioquia con bays 14/15/18 + pier + berth 3 (asset visual escenario operacional)
+• Mapa Puerto Antioquia con bays 14/15/18 + pier + pre-cooling chamber + genset + berth 3 (asset visual usado en rehearsal yard walk)
+• Mission Brief 'Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · The CARIBBEAN STAR Departure' (escenario auténtico viernes 4pm Puerto Antioquia · 80 reefer containers Cavendish bananas hacia Hamburgo · panel evaluador 3 personas · cuadrillas 6 personas · 90 min en 3 fases internas)
+• Pocket card laminada continuidad profesional post-programa (80 términos canon RA1+RA2+RA3+RA4 + 5 master functions IMARPOR + QR acceso material consolidado)
+• Pocket cards laminadas SMCP Quick Reference + NATO Phonetic Alphabet (asset operacional cuadrilla durante VHF)
+• Pre-Shipment Cold Chain Audit Checklist template (1 página A4 · banana cold chain Puerto Antioquia · campos en inglés · base para visitor checklist cuadrilla)
+• Reefer Temperature Log (24h tracking · setpoint validation · alarmas · base para VHF script + handover meeting)
+• Rúbrica ABP capstone 6 criterios C01-C13 (C01-aplicado vocab 15pts + C03+C04-aplicado SMCP/VHF 20pts + C05-aplicado tripartite handover 20pts + C06-aplicado master functions 15pts + C08-PRIMARIO estructuras ocupacionales 20pts + cold chain integrity P6 10pts · ponderación 100 puntos · ≥70 PASS)
+• Rúbrica ABP capstone 6 criterios C01-C13 (instrumento canon evaluador panel · ponderación 100 puntos · ≥70 PASS · descriptores nivelados A1.3 a A2.1+)
+• SMCP Quick Reference card (8 message markers + standard responses + NATO Phonetic Alphabet · base para VHF script cuadrilla)</t>
+        </is>
+      </c>
+      <c r="N20" s="91" t="inlineStr">
+        <is>
+          <t>Sergio Cortés Perdomo (instructor líder · arquitecto pedagógico FPI SENA Bilingüismo · responsable tripartita ABP capstone) + Diana Samboni (co-instructora · soporte didáctico + acompañamiento E1-E6) · Co-instructores invitados al universo operacional: Pipa (refrigeration technician · co-instructor experiencial VHF/SMCP) + Hernando Ospina (panel evaluador externo capstone E-Misión S12) · Personajes operacionales encarnados (cuando logística lo permite): Mariana Suárez (cold chain coordinator · arquetipo destino · narradora ICA Certificate spark + panel S12) + Captain Lim Wei-Ming (panel S12 ev</t>
+        </is>
+      </c>
+      <c r="O20" s="89" t="inlineStr">
+        <is>
+          <t>Bloque BT · TRANSFERENCIA · Final Mission · Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · The CARIBBEAN STAR Departure · sesiones ['S11', 'S12'] · CEFR A2.1 (terminal)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="150" customFormat="1" customHeight="1" s="6">
-      <c r="A21" s="87" t="n"/>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>RA 4 DESCRIBIR EN INGLÉS LAS FUNCIONES HABITUALES Y/O MOMENTÁNEAS PROPIAS, DEL PERSONAL Y DE LOS ELEMENTOS QUE SE ENCUENTRAN EN EL CONTEXTO MARÍTIMO Y PORTUARIO, EN EL DESEMPEÑO DE SUS LABORES.</t>
-        </is>
-      </c>
-      <c r="C21" s="96" t="n"/>
-      <c r="D21" s="87" t="n"/>
-      <c r="E21" s="87" t="n"/>
-      <c r="F21" s="87" t="n"/>
-      <c r="G21" s="87" t="n"/>
-      <c r="H21" s="87" t="n"/>
-      <c r="I21" s="87" t="n"/>
-      <c r="J21" s="87" t="n"/>
-      <c r="K21" s="87" t="n"/>
-      <c r="L21" s="87" t="n"/>
-      <c r="M21" s="87" t="n"/>
-      <c r="N21" s="87" t="n"/>
+          <t>RA 4 DESCRIBIR EN INGLÉS LAS FUNCIONES HABITUALES Y/O MOMENTÁNEAS PROPIAS, DEL PERSONAL Y DE
+LOS ELEMENTOS QUE SE ENCUENTRAN EN EL CONTEXTO MARÍTIMO Y PORTUARIO, EN EL DESEMPEÑO DE
+SUS LABORES.</t>
+        </is>
+      </c>
       <c r="O21" s="43" t="n"/>
-      <c r="P21" s="72" t="n"/>
     </row>
     <row r="22" ht="15" customFormat="1" customHeight="1" s="6">
       <c r="G22" s="62" t="n"/>
-      <c r="H22" s="97" t="n">
-        <v>72</v>
-      </c>
-      <c r="I22" s="97" t="n">
-        <v>28</v>
+      <c r="H22" s="6">
+        <f>SUM(H15:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="6">
+        <f>SUM(I15:I21)</f>
+        <v/>
       </c>
       <c r="J22" s="9" t="n"/>
     </row>
@@ -2194,12 +2463,10 @@
       <c r="J38" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="G15:G21"/>
+  <mergeCells count="28">
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="B13:C14"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="M15:M21"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="G13:G14"/>
@@ -2208,41 +2475,23 @@
     <mergeCell ref="E9:P9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="E11:H11"/>
-    <mergeCell ref="D15:D21"/>
     <mergeCell ref="E6:P6"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="O15:P17"/>
-    <mergeCell ref="O20:P20"/>
     <mergeCell ref="D13:D14"/>
-    <mergeCell ref="H15:H21"/>
-    <mergeCell ref="N15:N21"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="O13:P14"/>
-    <mergeCell ref="A15:A21"/>
     <mergeCell ref="E7:P7"/>
     <mergeCell ref="F13:F14"/>
-    <mergeCell ref="I15:I21"/>
-    <mergeCell ref="K15:K21"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="O21:P21"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="K13:K14"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="O18:P19"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B18:C19"/>
     <mergeCell ref="E10:H10"/>
-    <mergeCell ref="F15:F21"/>
     <mergeCell ref="A2:O3"/>
-    <mergeCell ref="B15:C17"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="L13:N13"/>
     <mergeCell ref="E8:P8"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="J15:J21"/>
-    <mergeCell ref="L15:L21"/>
-    <mergeCell ref="E15:E21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="27" horizontalDpi="1200" verticalDpi="1200"/>

--- a/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
+++ b/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
@@ -1793,10 +1793,14 @@
       </c>
       <c r="G15" s="92" t="inlineStr">
         <is>
-          <t>• #1 S1 (pm-2-1 · actitudinal · 1.0h) — Reflexionar sobre el miedo operacional al inglés VHF mediante video testimonio dramatizado de Manuel Padilla activando interés afectivo en operaciones cold chain Puerto Antioquia.
-• #2 S1 (pm-2-1 · actitudinal · 1.0h) — Reflexionar sobre el arquetipo destino cold chain coordinator mediante artefacto ICA Phytosanitary Certificate firmado por Mariana Suárez activando proyección afectiva operaciones bilingües.
-• #3 S1 (pm-2-2 · cognitiva · 1.5h) — Diagnosticar el reconocimiento léxico portuario reefer mediante galería visual diagnóstica y KWL bilingüe activando saberes operacionales previos.
-• #4 S1 (pm-2-2 · cognitiva · 1.5h) — Diagnosticar el baseline auditivo SMCP mediante audio VHF auténtico de 90 segundos y checklist binaria triangulada sin enseñar frases nuevas.</t>
+          <t>1. Actividad actitudinal:
+Reflexionar sobre el miedo operacional al inglés VHF mediante video testimonio dramatizado de Manuel Padilla activando interés afectivo en operaciones cold chain Puerto Antioquia.
+2. Actividad actitudinal:
+Reflexionar sobre el arquetipo destino cold chain coordinator mediante artefacto ICA Phytosanitary Certificate firmado por Mariana Suárez activando proyección afectiva operaciones bilingües.
+3. Actividad cognitiva:
+Diagnosticar el reconocimiento léxico portuario reefer mediante galería visual diagnóstica y KWL bilingüe activando saberes operacionales previos.
+4. Actividad cognitiva:
+Diagnosticar el baseline auditivo SMCP mediante audio VHF auténtico de 90 segundos y checklist binaria triangulada sin enseñar frases nuevas.</t>
         </is>
       </c>
       <c r="H15" s="89" t="inlineStr">
@@ -1811,12 +1815,23 @@
       </c>
       <c r="J15" s="92" t="inlineStr">
         <is>
-          <t>• (N/A — bloque APERTURA NO produce evidencias formales por diseño · rationale_sin_evidencias)</t>
+          <t>(N/A — bloque APERTURA NO produce evidencias formales por diseño · rationale_sin_evidencias)</t>
         </is>
       </c>
       <c r="K15" s="92" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 1.
+Estrategia didáctica: Aprendizaje colaborativo + Aprendizaje basado en experiencias
+Técnica Didáctica: Lluvia de ideas + Narrativa y testimonio
+Actividad 2.
+Estrategia didáctica: Aprendizaje colaborativo + Aprendizaje basado en experiencias
+Técnica Didáctica: Estudio de caso + Narrativa y testimonio
+Actividad 3.
+Estrategia didáctica: Trabajo colaborativo + Aprendizaje colaborativo
+Técnica Didáctica: Investigación guiada + Lluvia de ideas
+Actividad 4.
+Estrategia didáctica: Trabajo colaborativo + Content-Based Learning
+Técnica Didáctica: Investigación guiada + Análisis de casos</t>
         </is>
       </c>
       <c r="L15" s="89" t="inlineStr">
@@ -1892,12 +1907,18 @@
       </c>
       <c r="G16" s="91" t="inlineStr">
         <is>
-          <t>• #7 S3 (pm-2-3 · cognitiva · 4h) — Reconocer vocabulario portuario y partes del barco en el Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia' aplicando DRTA + K-W-L + Story Map.
-• #10 S4 (pm-2-4 · procedimental · 4.5h) — Producir un Inspection Report técnico de una página sobre el walk-around del bay 14 del MV CARIBBEAN STAR aplicando vocabulario portuario y estructuras gramaticales A1.2-A1.3.
-• #5 S2 (pm-2-5 · cognitiva · 2.5h) — Mapear 20 términos canon RA1 sobre partes del barco, tipos de vessels, equipamiento y profesiones portuarias mediante Word Wall Active y mapa semántico colaborativo.
-• #8 S3 (pm-2-6 · cognitiva · 1.5h) — Reforzar comprensión auditiva del vocabulario portuario y bay counts en audio Reefer Yard Walk de Yurlenis.
-• #6 S2 (pm-2-10 · cognitiva · 2.5h) — Inducir el patrón canon de verb to be, demostrativos this/that/these/those y plurales -s/-es a partir de un corpus reefer y formular la regla en propias palabras.
-• #12 S4 (pm-4-2 · cognitiva · 1.0h) — Diseñar el banco proto de ítems Vocabulary y Reading cara RA1 del Cuestionario Consolidado E6 mediante curaduría colaborativa de 6-8 ítems sobre vocabulario portuario.</t>
+          <t>5. Actividad cognitiva:
+Mapear 20 términos canon RA1 sobre partes del barco, tipos de vessels, equipamiento y profesiones portuarias mediante Word Wall Active y mapa semántico colaborativo.
+6. Actividad cognitiva:
+Inducir el patrón canon de verb to be, demostrativos this/that/these/those y plurales -s/-es a partir de un corpus reefer y formular la regla en propias palabras.
+7. Actividad cognitiva:
+Reconocer vocabulario portuario y partes del barco en el Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia' aplicando DRTA + K-W-L + Story Map.
+8. Actividad cognitiva:
+Reforzar comprensión auditiva del vocabulario portuario y bay counts en audio Reefer Yard Walk de Yurlenis.
+10. Actividad procedimental:
+Producir un Inspection Report técnico de una página sobre el walk-around del bay 14 del MV CARIBBEAN STAR aplicando vocabulario portuario y estructuras gramaticales A1.2-A1.3.
+12. Actividad cognitiva:
+Diseñar el banco proto de ítems Vocabulary y Reading cara RA1 del Cuestionario Consolidado E6 mediante curaduría colaborativa de 6-8 ítems sobre vocabulario portuario.</t>
         </is>
       </c>
       <c r="H16" s="91" t="inlineStr">
@@ -1912,13 +1933,36 @@
       </c>
       <c r="J16" s="91" t="inlineStr">
         <is>
-          <t>• [?] Comprensión lectora del Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia · Meet the Reefer Crew' (vocabulario portuario · partes del barco · oficios bananeros del cast operacional) · tipo=Conocimiento · instrumento=?
-• [?] Inspection Report técnico del walk-around bay 14 MV CARIBBEAN STAR (vocabulario portuario · partes del barco · oficios bananeros · verb to be · plurales · imperative en safety commands · preposición IN para location) · tipo=Producto · instrumento=?</t>
+          <t>[Actividad 7 · E1]
+Evidencia de conocimiento: Comprensión lectora del Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia · Meet the Reefer Crew' (vocabulario portuario · partes del barco · oficios bananeros del cast operacional)
+Técnica de evaluación: Preguntas
+Instrumento de evaluación No 1: Cuestionario
+[Actividad 10 · E2]
+Evidencia de producto: Inspection Report técnico del walk-around bay 14 MV CARIBBEAN STAR (vocabulario portuario · partes del barco · oficios bananeros · verb to be · plurales · imperative en safety commands · preposición IN para location)
+Técnica de evaluación: Verificación de producto
+Instrumento de evaluación No 2: Lista de verificación</t>
         </is>
       </c>
       <c r="K16" s="91" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 5.
+Estrategia didáctica: Aprendizaje colaborativo + Content-Based Learning
+Técnica Didáctica: Mapas conceptuales + Jigsaw
+Actividad 6.
+Estrategia didáctica: Investigación guiada + Aprendizaje colaborativo
+Técnica Didáctica: Análisis de casos + Taller
+Actividad 7.
+Estrategia didáctica: Aprendizaje colaborativo + Content-Based Learning
+Técnica Didáctica: Investigación guiada + Jigsaw
+Actividad 8.
+Estrategia didáctica: Aprendizaje colaborativo
+Técnica Didáctica: Investigación guiada + Práctica de campo
+Actividad 10.
+Estrategia didáctica: Aprendizaje colaborativo + TBLT
+Técnica Didáctica: Taller + Análisis de casos
+Actividad 12.
+Estrategia didáctica: Aprendizaje colaborativo + Investigación guiada
+Técnica Didáctica: Taller + Análisis de casos</t>
         </is>
       </c>
       <c r="L16" s="91" t="inlineStr">
@@ -1999,11 +2043,16 @@
       </c>
       <c r="G17" s="91" t="inlineStr">
         <is>
-          <t>• #14 S5 (pm-2-5 · cognitiva · 1.5h) — Instalar 20 términos canon SMCP RA2 sobre message markers, standard responses y NATO Phonetic mediante Word Wall categorizado y articulación phonics light cero-tolerancia.
-• #13 S5 (pm-2-6 · procedimental · 3.0h) — Identificar mensajes correctos y distractores SMCP en audio VHF auténtico de Captain Lim Wei-Ming según protocolo OMI.
-• #15 S6 (pm-2-8 · procedimental · 2.5h) — Aplicar respuestas estandarizadas SMCP y deletreo NATO Phonetic en role-play VHF con Captain Lim del MV CARIBBEAN STAR.
-• #15 S5 (pm-2-10 · cognitiva · 1.0h) — Descubrir y automatizar la sintaxis SMCP IMO de message markers, standard responses, NATO Phonetic y protocolo Over/Out mediante consciousness-raising y drill cero-tolerancia.
-• #16 S6 (pm-4-2 · cognitiva · 3.0h) — Demostrar dominio integrado consolidado de Reading + Writing + Listening + Vocabulary + Grammar mediante el Cuestionario Consolidado E6 de 25 ítems con criterio PASS ≥ 70%.</t>
+          <t>13. Actividad procedimental:
+Identificar mensajes correctos y distractores SMCP en audio VHF auténtico de Captain Lim Wei-Ming según protocolo OMI.
+14. Actividad cognitiva:
+Instalar 20 términos canon SMCP RA2 sobre message markers, standard responses y NATO Phonetic mediante Word Wall categorizado y articulación phonics light cero-tolerancia.
+15. Actividad procedimental:
+Aplicar respuestas estandarizadas SMCP y deletreo NATO Phonetic en role-play VHF con Captain Lim del MV CARIBBEAN STAR.
+15. Actividad cognitiva:
+Descubrir y automatizar la sintaxis SMCP IMO de message markers, standard responses, NATO Phonetic y protocolo Over/Out mediante consciousness-raising y drill cero-tolerancia.
+16. Actividad cognitiva:
+Demostrar dominio integrado consolidado de Reading + Writing + Listening + Vocabulary + Grammar mediante el Cuestionario Consolidado E6 de 25 ítems con criterio PASS ≥ 70%.</t>
         </is>
       </c>
       <c r="H17" s="91" t="inlineStr">
@@ -2018,14 +2067,37 @@
       </c>
       <c r="J17" s="91" t="inlineStr">
         <is>
-          <t>• [?] Comprensión auditiva SMCP · identificación de message markers, standard responses y NATO Phonetic en VHF Arrival Exchange MV CARIBBEAN STAR · tipo=Desempeño · instrumento=?
-• [?] VHF Role-Play SMCP · respuestas críticas estandarizadas y deletreo NATO Phonetic con Captain Lim Wei-Ming y Bosun Andrés Mejía (zona accuracy-cero-tolerancia) · tipo=Desempeño · instrumento=?
-• [?] Cuestionario Consolidado S6 · 25 ítems · 5 skills × 5 puntos (Reading + Writing + Listening + Vocabulary + Grammar) · 4-way overlap C07 RA1+RA2+RA3+RA4 · ≥70% PASS · tipo=Conocimiento · instrumento=?</t>
+          <t>[Actividad 13 · E3]
+Evidencia de desempeño: Comprensión auditiva SMCP · identificación de message markers, standard responses y NATO Phonetic en VHF Arrival Exchange MV CARIBBEAN STAR
+Técnica de evaluación: Observación
+Instrumento de evaluación No 3: Lista de Chequeo
+[Actividad 15 · E4-parcial]
+Evidencia de desempeño: VHF Role-Play SMCP · respuestas críticas estandarizadas y deletreo NATO Phonetic con Captain Lim Wei-Ming y Bosun Andrés Mejía (zona accuracy-cero-tolerancia)
+Técnica de evaluación: Observación
+Instrumento de evaluación No 4: Escala de estimación
+[Actividad 16 · E6]
+Evidencia de conocimiento: Cuestionario Consolidado S6 · 25 ítems · 5 skills × 5 puntos (Reading + Writing + Listening + Vocabulary + Grammar) · 4-way overlap C07 RA1+RA2+RA3+RA4 · ≥70% PASS
+Técnica de evaluación: Preguntas
+Instrumento de evaluación No 6: Cuestionario</t>
         </is>
       </c>
       <c r="K17" s="91" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 13.
+Estrategia didáctica: TBLT + Aprendizaje colaborativo
+Técnica Didáctica: Práctica de campo + Jigsaw
+Actividad 14.
+Estrategia didáctica: Aprendizaje colaborativo + Simulación
+Técnica Didáctica: Jigsaw + Práctica de campo
+Actividad 15.
+Estrategia didáctica: Juego de roles + Simulación
+Técnica Didáctica: Role play + Dramatización
+Actividad 15.
+Estrategia didáctica: Aprendizaje basado en tareas + Simulación
+Técnica Didáctica: Análisis de casos + Taller
+Actividad 16.
+Estrategia didáctica: Aprendizaje basado en problemas
+Técnica Didáctica: Taller + Análisis de casos</t>
         </is>
       </c>
       <c r="L17" s="91" t="inlineStr">
@@ -2107,11 +2179,16 @@
       </c>
       <c r="G18" s="91" t="inlineStr">
         <is>
-          <t>• #19 S7 (pm-2-5 · cognitiva · 1.5h) — Consolidar 20 términos canon RA3 sobre commands a destinatarios, imperativos de seguridad y modal verbs mediante Word Wall, semantic gradients y jigsaw command-addressee.
-• #17 S7 (pm-2-6 · cognitiva · 1.0h) — Anticipar y reconstruir órdenes y modal verbs del Berthing Tripartito mediante Predictive Listening y Dictogloss ligero.
-• #21 S8 (pm-2-8 · procedimental · 4.0h) — Coordinar berthing tripartito simultáneo del MV CARIBBEAN STAR aplicando commands, imperative, modals y extensiones C05 (condicional, pasiva, presente perfecto).
-• #22 S8 (pm-2-9 · cognitiva · 1.5h) — Activar las 5 funciones comunicativas canon RA3 mediante drill de function cards previo al Berthing Tripartito Simultáneo.
-• #20 S7 (pm-2-10 · cognitiva · 2.0h) — Consolidar commands a destinatarios, imperative, present simple Wh-questions y modals gradient con tres extensiones C05 (conditional t1, voz pasiva, presente perfecto) mediante rule formulation, transformation drills y reasoning-gap berthing.</t>
+          <t>17. Actividad cognitiva:
+Anticipar y reconstruir órdenes y modal verbs del Berthing Tripartito mediante Predictive Listening y Dictogloss ligero.
+19. Actividad cognitiva:
+Consolidar 20 términos canon RA3 sobre commands a destinatarios, imperativos de seguridad y modal verbs mediante Word Wall, semantic gradients y jigsaw command-addressee.
+20. Actividad cognitiva:
+Consolidar commands a destinatarios, imperative, present simple Wh-questions y modals gradient con tres extensiones C05 (conditional t1, voz pasiva, presente perfecto) mediante rule formulation, transformation drills y reasoning-gap berthing.
+21. Actividad procedimental:
+Coordinar berthing tripartito simultáneo del MV CARIBBEAN STAR aplicando commands, imperative, modals y extensiones C05 (condicional, pasiva, presente perfecto).
+22. Actividad cognitiva:
+Activar las 5 funciones comunicativas canon RA3 mediante drill de function cards previo al Berthing Tripartito Simultáneo.</t>
         </is>
       </c>
       <c r="H18" s="91" t="inlineStr">
@@ -2126,12 +2203,29 @@
       </c>
       <c r="J18" s="91" t="inlineStr">
         <is>
-          <t>• [?] Berthing Tripartito Simultáneo del MV CARIBBEAN STAR · coordinación 5 actores aplicando 4 saberes canon RA3 + 3 extensiones C05 emergentes (zona accuracy+fluency híbrida) · tipo=Desempeño · instrumento=?</t>
+          <t>[Actividad 21 · E4-final]
+Evidencia de desempeño: Berthing Tripartito Simultáneo del MV CARIBBEAN STAR · coordinación 5 actores aplicando 4 saberes canon RA3 + 3 extensiones C05 emergentes (zona accuracy+fluency híbrida)
+Técnica de evaluación: Observación
+Instrumento de evaluación No 4: Escala de estimación</t>
         </is>
       </c>
       <c r="K18" s="91" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 17.
+Estrategia didáctica: Aprendizaje colaborativo
+Técnica Didáctica: Investigación guiada
+Actividad 19.
+Estrategia didáctica: Aprendizaje colaborativo + Simulación
+Técnica Didáctica: Jigsaw + Mapas conceptuales
+Actividad 20.
+Estrategia didáctica: Aprendizaje basado en tareas + Simulación
+Técnica Didáctica: Análisis de casos + Taller
+Actividad 21.
+Estrategia didáctica: Juego de roles + Aprendizaje basado en proyectos
+Técnica Didáctica: Role play + Simulación + Dramatización
+Actividad 22.
+Estrategia didáctica: Aprendizaje colaborativo
+Técnica Didáctica: Juego de roles + Think-Pair-Share</t>
         </is>
       </c>
       <c r="L18" s="91" t="inlineStr">
@@ -2211,11 +2305,16 @@
       </c>
       <c r="G19" s="91" t="inlineStr">
         <is>
-          <t>• #24 S9 (pm-2-5 · cognitiva · 1.0h) — Cerrar Toolbelt cuádruple con 20 términos canon RA4 sobre lugares en puerto, condiciones meteo, contenedorización y maniobras mediante Word Wall categorizado y Quizlet pareo.
-• #23 S9 (pm-2-6 · cognitiva · 0.5h) — Analizar y categorizar las 5 master functions IMARPOR del Role Carousel Briefing audio de Mariana, Carolina y Yurlenis.
-• #25 S9 (pm-2-9 · procedimental · 3.5h) — Ejecutar las 5 master functions IMARPOR mediante Role Carousel de 5 estaciones rotativas con conectores discursivos canon C06.
-• #25 S9 (pm-2-10 · cognitiva · 1.0h) — Producir tag questions, present progressive con prepositional phrases y quantifiers definidos/indefinidos mediante data-based discovery, sentence building y chain story descriptiva pre-Role Carousel.
-• #28 S10 (pm-2-10 · cognitiva · 5.0h) — Integrar las estructuras gramaticales de B1+B2+B3+B4 en un rehearsal cross-RAP del Pre-Departure Banana Reefer Compliance Check con feedback formativo cohesión gramatical no calificativo.</t>
+          <t>23. Actividad cognitiva:
+Analizar y categorizar las 5 master functions IMARPOR del Role Carousel Briefing audio de Mariana, Carolina y Yurlenis.
+24. Actividad cognitiva:
+Cerrar Toolbelt cuádruple con 20 términos canon RA4 sobre lugares en puerto, condiciones meteo, contenedorización y maniobras mediante Word Wall categorizado y Quizlet pareo.
+25. Actividad procedimental:
+Ejecutar las 5 master functions IMARPOR mediante Role Carousel de 5 estaciones rotativas con conectores discursivos canon C06.
+25. Actividad cognitiva:
+Producir tag questions, present progressive con prepositional phrases y quantifiers definidos/indefinidos mediante data-based discovery, sentence building y chain story descriptiva pre-Role Carousel.
+28. Actividad cognitiva:
+Integrar las estructuras gramaticales de B1+B2+B3+B4 en un rehearsal cross-RAP del Pre-Departure Banana Reefer Compliance Check con feedback formativo cohesión gramatical no calificativo.</t>
         </is>
       </c>
       <c r="H19" s="91" t="inlineStr">
@@ -2230,12 +2329,29 @@
       </c>
       <c r="J19" s="91" t="inlineStr">
         <is>
-          <t>• [?] Producción funcional descriptiva en Role Carousel · 5 master functions IMARPOR con conectores discursivos canon en escenario banana cold chain Puerto Antioquia · tipo=Desempeño · instrumento=?</t>
+          <t>[Actividad 25 · E5]
+Evidencia de desempeño: Producción funcional descriptiva en Role Carousel · 5 master functions IMARPOR con conectores discursivos canon en escenario banana cold chain Puerto Antioquia
+Técnica de evaluación: Observación
+Instrumento de evaluación No 5: Escala de estimación</t>
         </is>
       </c>
       <c r="K19" s="91" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 23.
+Estrategia didáctica: Aprendizaje basado en tareas
+Técnica Didáctica: Análisis de casos
+Actividad 24.
+Estrategia didáctica: Aprendizaje colaborativo + Trabajo colaborativo
+Técnica Didáctica: Mapas conceptuales + Práctica de campo
+Actividad 25.
+Estrategia didáctica: Juego de roles + Aprendizaje colaborativo
+Técnica Didáctica: Role play + Práctica de campo
+Actividad 25.
+Estrategia didáctica: Aprendizaje basado en tareas + Aprendizaje colaborativo
+Técnica Didáctica: Análisis de casos + Taller
+Actividad 28.
+Estrategia didáctica: Simulación + Aprendizaje basado en tareas
+Técnica Didáctica: Práctica de campo + Conversatorio</t>
         </is>
       </c>
       <c r="L19" s="91" t="inlineStr">
@@ -2314,11 +2430,16 @@
       </c>
       <c r="G20" s="91" t="inlineStr">
         <is>
-          <t>• #29 S11 (pm-3-5 · cognitiva · 1.5h) — Comprender el Mission Brief Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover MV CARIBBEAN STAR confirmando role assignment y rúbrica ABP capstone.
-• #30 S11 (pm-3-5 · cognitiva · 1.5h) — Preparar visitor checklist + VHF script SMCP + handover pitch outline integrando vocabulario y estructuras de los 4 RAPs para el capstone.
-• #31 S11 (pm-3-5 · procedimental · 3.0h) — Ensayar la jornada completa de 90 minutos cuadrilla por cuadrilla recibiendo feedback formativo NO calificativo sobre SMCP accuracy y handover fluency.
-• #32 S12 (pm-3-5 · procedimental · 3.0h) — Ejecutar la jornada operacional Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover de 90 minutos por cuadrilla ante panel evaluador externo aplicando los 4 RAPs integrados.
-• #33 S12 (pm-3-5 · actitudinal · 3.0h) — Reflexionar sobre el journey CEFR A1.2 → A2.1 mediante debrief panel + entrega de diplomas + ritual de cierre programa cold chain integrity.</t>
+          <t>29. Actividad cognitiva:
+Comprender el Mission Brief Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover MV CARIBBEAN STAR confirmando role assignment y rúbrica ABP capstone.
+30. Actividad cognitiva:
+Preparar visitor checklist + VHF script SMCP + handover pitch outline integrando vocabulario y estructuras de los 4 RAPs para el capstone.
+31. Actividad procedimental:
+Ensayar la jornada completa de 90 minutos cuadrilla por cuadrilla recibiendo feedback formativo NO calificativo sobre SMCP accuracy y handover fluency.
+32. Actividad procedimental:
+Ejecutar la jornada operacional Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover de 90 minutos por cuadrilla ante panel evaluador externo aplicando los 4 RAPs integrados.
+33. Actividad actitudinal:
+Reflexionar sobre el journey CEFR A1.2 → A2.1 mediante debrief panel + entrega de diplomas + ritual de cierre programa cold chain integrity.</t>
         </is>
       </c>
       <c r="H20" s="91" t="inlineStr">
@@ -2333,12 +2454,29 @@
       </c>
       <c r="J20" s="91" t="inlineStr">
         <is>
-          <t>• [?] Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · Performance Panel MV CARIBBEAN STAR (capstone integrador 4 RAPs · 90 min/cuadrilla · panel evaluador externo 3 personas Captain Lim + Mariana + Hernando) · tipo=Desempeño · instrumento=?</t>
+          <t>[Actividad 32 · E-Misión]
+Evidencia de desempeño: Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover · Performance Panel MV CARIBBEAN STAR (capstone integrador 4 RAPs · 90 min/cuadrilla · panel evaluador externo 3 personas Captain Lim + Mariana + Hernando)
+Técnica de evaluación: Observación
+Instrumento de evaluación No None: Rúbrica ABP capstone</t>
         </is>
       </c>
       <c r="K20" s="91" t="inlineStr">
         <is>
-          <t>• (heredar de logistics_box pm-3-2 downstream)</t>
+          <t>Actividad 29.
+Estrategia didáctica: Aprendizaje basado en proyectos + ABP
+Técnica Didáctica: Conversatorio + Análisis de casos
+Actividad 30.
+Estrategia didáctica: Aprendizaje basado en proyectos + Aprendizaje colaborativo
+Técnica Didáctica: Investigación guiada + Taller
+Actividad 31.
+Estrategia didáctica: ABP + Simulación
+Técnica Didáctica: Práctica de campo + Role play
+Actividad 32.
+Estrategia didáctica: ABP + Simulación
+Técnica Didáctica: Práctica de campo + Panel discussion
+Actividad 33.
+Estrategia didáctica: Aprendizaje colaborativo + Aprendizaje basado en experiencias
+Técnica Didáctica: Conversatorio + Mesa redonda</t>
         </is>
       </c>
       <c r="L20" s="91" t="inlineStr">

--- a/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
+++ b/runs/IMARPOR-CC-2026-04-30-V2/pm-2-11-GFPI-F-134-V04.xlsx
@@ -1762,7 +1762,7 @@
       </c>
       <c r="O14" s="88" t="n"/>
     </row>
-    <row r="15" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="15" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A15" s="89" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -1788,6 +1788,11 @@
       <c r="F15" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">
+— PER-ACTIVITY (heredados AC v3.1 · 4 cards) —
+  • #1 (actitudinal): Reflexiona sobre el miedo operacional al inglés VHF.
+  • #2 (actitudinal): Reflexiona sobre el arquetipo destino cold chain coordinator.
+  • #3 (cognitiva): Identifica el reconocimiento léxico portuario reefer.
+  • #4 (cognitiva): Identifica el baseline auditivo SMCP.
 [Rationale]: APERTURA NO produce evidencias formales · criterios canon = activación afectiva + diagnóstico baseline</t>
         </is>
       </c>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="J15" s="92" t="inlineStr">
         <is>
-          <t>(N/A — bloque APERTURA NO produce evidencias formales por diseño · rationale_sin_evidencias)</t>
+          <t>(N/A — APERTURA NO produce evidencias formales)</t>
         </is>
       </c>
       <c r="K15" s="92" t="inlineStr">
@@ -1864,7 +1869,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="16" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A16" s="91" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -1902,7 +1907,14 @@
 — CANON SISTEMA C01-C08 —
   • C01
   • C02
-  • C07</t>
+  • C07
+— PER-ACTIVITY (heredados AC v3.1 · 6 cards) —
+  • #5 (cognitiva): Identifica 20 términos canon RA1 sobre partes del barco, tipos de vessels, equipamiento y profesiones portuarias.
+  • #6 (cognitiva): Reconoce el patrón canon de verb to be, demostrativos this/that/these/those y plurales -s/-es a partir de un corpus reefer y formular la regla en propias palabras.
+  • #7 (cognitiva): Reconoce vocabulario portuario y partes del barco en el Story A 'MV CARIBBEAN STAR Arrives at Puerto Antioquia'.
+  • #8 (cognitiva): Refuerza comprensión auditiva del vocabulario portuario y bay counts en audio Reefer Yard Walk de Yurlenis.
+  • #10 (procedimental): Produce un Inspection Report técnico de una página sobre el walk-around del bay 14 del MV CARIBBEAN STAR aplicando vocabulario portuario y estructuras gramaticales A1.2-A1.3.
+  • #12 (cognitiva): Identifica el banco proto de ítems Vocabulary y Reading cara RA1 del Cuestionario Consolidado E6.</t>
         </is>
       </c>
       <c r="G16" s="91" t="inlineStr">
@@ -2003,7 +2015,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="17" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A17" s="91" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -2038,7 +2050,12 @@
 — CANON SISTEMA C01-C08 —
   • C03
   • C04
-  • C07</t>
+  • C07
+— PER-ACTIVITY (heredados AC v3.1 · 4 cards) —
+  • #13 (procedimental): Aplica mensajes correctos y distractores SMCP en audio VHF auténtico de Captain Lim Wei-Ming según protocolo OMI.
+  • #14 (cognitiva): Identifica 20 términos canon SMCP RA2 sobre message markers, standard responses y NATO Phonetic.
+  • #15 (cognitiva): Identifica y automatizar la sintaxis SMCP IMO de message markers, standard responses, NATO Phonetic y protocolo Over/Out.
+  • #16 (cognitiva): Identifica dominio integrado consolidado de Reading + Writing + Listening + Vocabulary + Grammar.</t>
         </is>
       </c>
       <c r="G17" s="91" t="inlineStr">
@@ -2137,7 +2154,7 @@
       </c>
       <c r="U17" s="7" t="n"/>
     </row>
-    <row r="18" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="18" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A18" s="91" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -2174,7 +2191,13 @@
   • C04
   • C05
   • C06
-  • C07</t>
+  • C07
+— PER-ACTIVITY (heredados AC v3.1 · 5 cards) —
+  • #17 (cognitiva): Anticipa y reconstruir órdenes y modal verbs del Berthing Tripartito.
+  • #19 (cognitiva): Reconoce 20 términos canon RA3 sobre commands a destinatarios, imperativos de seguridad y modal verbs.
+  • #20 (cognitiva): Reconoce commands a destinatarios, imperative, present simple Wh-questions y modals gradient con tres extensiones C05 (conditional t1, voz pasiva, presente perfecto).
+  • #21 (procedimental): Coordina berthing tripartito simultáneo del MV CARIBBEAN STAR.
+  • #22 (cognitiva): Identifica las 5 funciones comunicativas canon RA3.</t>
         </is>
       </c>
       <c r="G18" s="91" t="inlineStr">
@@ -2262,7 +2285,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="19" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A19" s="91" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -2300,7 +2323,12 @@
   • DESCRIBE EN INGLÉS PROCESOS Y FUNCIONES PROPIAS DEL CONTEXTO MARÍTIMO Y PORTUARIO.
 — CANON SISTEMA C01-C08 —
   • C06
-  • C07</t>
+  • C07
+— PER-ACTIVITY (heredados AC v3.1 · 4 cards) —
+  • #23 (cognitiva): Analiza y categorizar las 5 master functions IMARPOR del Role Carousel Briefing audio de Mariana, Carolina y Yurlenis.
+  • #24 (cognitiva): Identifica Toolbelt cuádruple con 20 términos canon RA4 sobre lugares en puerto, condiciones meteo, contenedorización y maniobras.
+  • #25 (cognitiva): Identifica tag questions, present progressive con prepositional phrases y quantifiers definidos/indefinidos.
+  • #28 (cognitiva): Relaciona las estructuras gramaticales de B1+B2+B3+B4 en un rehearsal cross-RAP del Pre-Departure Banana Reefer Compliance Check con feedback formativo cohesión gramatical no calificativo.</t>
         </is>
       </c>
       <c r="G19" s="91" t="inlineStr">
@@ -2388,7 +2416,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="600" customFormat="1" customHeight="1" s="6">
+    <row r="20" ht="700" customFormat="1" customHeight="1" s="6">
       <c r="A20" s="91" t="inlineStr">
         <is>
           <t>INTERACTUAR CON OTROS EN IDIOMA EXTRANJERO SEGÚN ESTIPULACIONES DEL MARCO COMÚN EUROPEO DE REFERENCIA PARA IDIOMAS.</t>
@@ -2425,7 +2453,13 @@
           <t>— SOFÍA SENA (matriz v1.3) —
   • (integra los 7 criterios SOFÍA cubiertos en B1-B4 vía evidencia E-Misión ABP)
 — CANON SISTEMA C01-C08 —
-  • C08</t>
+  • C08
+— PER-ACTIVITY (heredados AC v3.1 · 5 cards) —
+  • #29 (cognitiva): Comprende el Mission Brief Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover MV CARIBBEAN STAR confirmando role assignment y rúbrica ABP capstone.
+  • #30 (cognitiva): Reconoce visitor checklist + VHF script SMCP + handover pitch outline integrando vocabulario y estructuras de los 4 RAPs para el capstone.
+  • #31 (procedimental): Aplica la jornada completa de 90 minutos cuadrilla por cuadrilla recibiendo feedback formativo NO calificativo sobre SMCP accuracy y handover fluency.
+  • #32 (procedimental): Ejecuta la jornada operacional Pre-Departure Banana Reefer Compliance Check &amp; Tripartite Handover de 90 minutos por cuadrilla ante panel evaluador externo.
+  • #33 (actitudinal): Reflexiona sobre el journey CEFR A1.2 → A2.1.</t>
         </is>
       </c>
       <c r="G20" s="91" t="inlineStr">
